--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1363,7 +1363,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="934">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2731,9 +2731,6 @@
     <t>1669: source value from PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
-    <t>Pharmacy: quantity</t>
-  </si>
-  <si>
     <t>MedicationRequest.dispenseRequest.quantity.comparator</t>
   </si>
   <si>
@@ -2759,9 +2756,6 @@
   </si>
   <si>
     <t>1670: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
-  </si>
-  <si>
-    <t>Pharmacy: daysSupply</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Substitutions</t>
@@ -3276,7 +3270,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="175.39453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="43.37109375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -16824,7 +16818,7 @@
         <v>651</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>84</v>
+        <v>651</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>84</v>
@@ -18334,7 +18328,7 @@
         <v>690</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>84</v>
+        <v>690</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>84</v>
@@ -19094,7 +19088,7 @@
         <v>690</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>84</v>
+        <v>690</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>84</v>
@@ -19348,7 +19342,7 @@
         <v>749</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>84</v>
+        <v>749</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>84</v>
@@ -22750,7 +22744,7 @@
         <v>84</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>874</v>
+        <v>84</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>84</v>
@@ -22770,10 +22764,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22898,10 +22892,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23024,10 +23018,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23150,10 +23144,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23278,10 +23272,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23307,13 +23301,13 @@
         <v>820</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>880</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="N160" t="s" s="2">
         <v>881</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>882</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -23363,7 +23357,7 @@
         <v>84</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
@@ -23378,22 +23372,22 @@
         <v>106</v>
       </c>
       <c r="AK160" t="s" s="2">
+        <v>882</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO160" t="s" s="2">
         <v>883</v>
       </c>
-      <c r="AL160" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM160" t="s" s="2">
+      <c r="AP160" t="s" s="2">
         <v>884</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO160" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="AP160" t="s" s="2">
-        <v>886</v>
       </c>
       <c r="AQ160" t="s" s="2">
         <v>84</v>
@@ -23404,10 +23398,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23430,13 +23424,13 @@
         <v>84</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="L161" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="M161" t="s" s="2">
         <v>888</v>
-      </c>
-      <c r="L161" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>890</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -23487,7 +23481,7 @@
         <v>84</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>82</v>
@@ -23517,7 +23511,7 @@
         <v>84</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="AQ161" t="s" s="2">
         <v>494</v>
@@ -23528,10 +23522,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23557,10 +23551,10 @@
         <v>799</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23611,7 +23605,7 @@
         <v>84</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23638,10 +23632,10 @@
         <v>84</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>84</v>
@@ -23652,10 +23646,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23776,10 +23770,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23902,10 +23896,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -24030,10 +24024,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24059,13 +24053,13 @@
         <v>612</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="M166" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="N166" t="s" s="2">
         <v>901</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>902</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>903</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -24094,10 +24088,10 @@
         <v>325</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>84</v>
@@ -24115,7 +24109,7 @@
         <v>84</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>93</v>
@@ -24142,24 +24136,24 @@
         <v>84</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="AQ166" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR166" t="s" s="2">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24185,10 +24179,10 @@
         <v>321</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -24218,10 +24212,10 @@
         <v>325</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>84</v>
@@ -24239,7 +24233,7 @@
         <v>84</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>82</v>
@@ -24266,24 +24260,24 @@
         <v>84</v>
       </c>
       <c r="AO167" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="AP167" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="AQ167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR167" t="s" s="2">
         <v>913</v>
-      </c>
-      <c r="AP167" t="s" s="2">
-        <v>914</v>
-      </c>
-      <c r="AQ167" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR167" t="s" s="2">
-        <v>915</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24306,13 +24300,13 @@
         <v>84</v>
       </c>
       <c r="K168" t="s" s="2">
+        <v>915</v>
+      </c>
+      <c r="L168" t="s" s="2">
+        <v>916</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>917</v>
-      </c>
-      <c r="L168" t="s" s="2">
-        <v>918</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>919</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -24363,7 +24357,7 @@
         <v>84</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -24387,13 +24381,13 @@
         <v>84</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="AQ168" t="s" s="2">
         <v>84</v>
@@ -24404,14 +24398,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -24430,16 +24424,16 @@
         <v>84</v>
       </c>
       <c r="K169" t="s" s="2">
+        <v>922</v>
+      </c>
+      <c r="L169" t="s" s="2">
+        <v>923</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>924</v>
       </c>
-      <c r="L169" t="s" s="2">
+      <c r="N169" t="s" s="2">
         <v>925</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>926</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>927</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -24489,7 +24483,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>82</v>
@@ -24519,7 +24513,7 @@
         <v>84</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>84</v>
@@ -24530,10 +24524,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24556,16 +24550,16 @@
         <v>84</v>
       </c>
       <c r="K170" t="s" s="2">
+        <v>928</v>
+      </c>
+      <c r="L170" t="s" s="2">
+        <v>929</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>930</v>
       </c>
-      <c r="L170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>931</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>932</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>933</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -24615,7 +24609,7 @@
         <v>84</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>82</v>
@@ -24639,13 +24633,13 @@
         <v>84</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="AQ170" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="936">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1363,7 +1363,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -2731,6 +2731,9 @@
     <t>1669: source value from PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
+    <t>Pharmacy: quantity</t>
+  </si>
+  <si>
     <t>MedicationRequest.dispenseRequest.quantity.comparator</t>
   </si>
   <si>
@@ -2756,6 +2759,9 @@
   </si>
   <si>
     <t>1670: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
+  </si>
+  <si>
+    <t>Pharmacy: daysSupply</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Substitutions</t>
@@ -3270,7 +3276,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="175.39453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="43.37109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -16818,7 +16824,7 @@
         <v>651</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>651</v>
+        <v>84</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>84</v>
@@ -18328,7 +18334,7 @@
         <v>690</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>690</v>
+        <v>84</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>84</v>
@@ -19088,7 +19094,7 @@
         <v>690</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>690</v>
+        <v>84</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>84</v>
@@ -19342,7 +19348,7 @@
         <v>749</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>749</v>
+        <v>84</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>84</v>
@@ -22744,7 +22750,7 @@
         <v>84</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>84</v>
+        <v>874</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>84</v>
@@ -22764,10 +22770,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22892,10 +22898,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23018,10 +23024,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23144,10 +23150,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23272,10 +23278,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23301,13 +23307,13 @@
         <v>820</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -23357,7 +23363,7 @@
         <v>84</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
@@ -23372,22 +23378,22 @@
         <v>106</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>84</v>
+        <v>884</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="AQ160" t="s" s="2">
         <v>84</v>
@@ -23398,10 +23404,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23424,13 +23430,13 @@
         <v>84</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -23481,7 +23487,7 @@
         <v>84</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>82</v>
@@ -23511,7 +23517,7 @@
         <v>84</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="AQ161" t="s" s="2">
         <v>494</v>
@@ -23522,10 +23528,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23551,10 +23557,10 @@
         <v>799</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23605,7 +23611,7 @@
         <v>84</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23632,10 +23638,10 @@
         <v>84</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>84</v>
@@ -23646,10 +23652,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23770,10 +23776,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23896,10 +23902,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -24024,10 +24030,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24053,13 +24059,13 @@
         <v>612</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -24088,10 +24094,10 @@
         <v>325</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>84</v>
@@ -24109,7 +24115,7 @@
         <v>84</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>93</v>
@@ -24136,24 +24142,24 @@
         <v>84</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="AQ166" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR166" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24179,10 +24185,10 @@
         <v>321</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -24212,10 +24218,10 @@
         <v>325</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>84</v>
@@ -24233,7 +24239,7 @@
         <v>84</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>82</v>
@@ -24260,24 +24266,24 @@
         <v>84</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="AQ167" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR167" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24300,13 +24306,13 @@
         <v>84</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -24357,7 +24363,7 @@
         <v>84</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -24381,13 +24387,13 @@
         <v>84</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="AQ168" t="s" s="2">
         <v>84</v>
@@ -24398,14 +24404,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -24424,16 +24430,16 @@
         <v>84</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -24483,7 +24489,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>82</v>
@@ -24513,7 +24519,7 @@
         <v>84</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>84</v>
@@ -24524,10 +24530,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24550,16 +24556,16 @@
         <v>84</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -24609,7 +24615,7 @@
         <v>84</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>82</v>
@@ -24633,13 +24639,13 @@
         <v>84</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="AQ170" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -866,7 +866,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/CMVFBoolean</t>
+    <t>http://va.gov/fhir/ConceptMap/Boolean</t>
   </si>
   <si>
     <t xml:space="preserve">ext-1
@@ -991,7 +991,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFOutMedRequestStatus</t>
+    <t>http://va.gov/fhir/ValueSet/OutMedRequestStatus</t>
   </si>
   <si>
     <t>799: terminologyMaps using VF_OutMedRequestStatus on PRESCRIPTION - STATUS (52-100)</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="938">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -611,6 +611,10 @@
     <t>Coding.system</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+MedicationRequestOutpatient-1746-1:if P then fixed value http://va.gov/terminology/vistaDefinedTerms/52-100 {null}</t>
+  </si>
+  <si>
     <t>1746-1: fixed value = http://va.gov/terminology/vistaDefinedTerms/52-100 case P</t>
   </si>
   <si>
@@ -660,6 +664,10 @@
   </si>
   <si>
     <t>Coding.code</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+MedicationRequestOutpatient-1746:if P then fixed value #active-parked {null}</t>
   </si>
   <si>
     <t>1746: fixed value = #active-parked when PRESCRIPTION - MAIL/WINDOW/PARK (52-11) case P</t>
@@ -5395,10 +5403,10 @@
         <v>84</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
@@ -5413,21 +5421,21 @@
         <v>84</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -5453,13 +5461,13 @@
         <v>153</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -5509,7 +5517,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -5539,21 +5547,21 @@
         <v>84</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5579,14 +5587,14 @@
         <v>114</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>84</v>
@@ -5635,7 +5643,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -5647,13 +5655,13 @@
         <v>84</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>106</v>
+        <v>209</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>84</v>
@@ -5665,21 +5673,21 @@
         <v>84</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5705,14 +5713,14 @@
         <v>153</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -5761,7 +5769,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5791,21 +5799,21 @@
         <v>84</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5828,19 +5836,19 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -5889,7 +5897,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5919,24 +5927,24 @@
         <v>84</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>84</v>
@@ -5958,13 +5966,13 @@
         <v>84</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -6056,7 +6064,7 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>152</v>
@@ -6180,7 +6188,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>159</v>
@@ -6304,7 +6312,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>163</v>
@@ -6347,7 +6355,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>84</v>
@@ -6430,7 +6438,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>170</v>
@@ -6456,7 +6464,7 @@
         <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>172</v>
@@ -6528,10 +6536,10 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>84</v>
@@ -6554,13 +6562,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>84</v>
@@ -6582,13 +6590,13 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6680,7 +6688,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>152</v>
@@ -6804,7 +6812,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>159</v>
@@ -6928,7 +6936,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>163</v>
@@ -6971,7 +6979,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>84</v>
@@ -7054,7 +7062,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>170</v>
@@ -7080,7 +7088,7 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>172</v>
@@ -7152,10 +7160,10 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>84</v>
@@ -7178,7 +7186,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>176</v>
@@ -7207,10 +7215,10 @@
         <v>153</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -7302,7 +7310,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>178</v>
@@ -7424,13 +7432,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -7452,16 +7460,16 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -7552,10 +7560,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7676,10 +7684,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7800,10 +7808,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7843,7 +7851,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>84</v>
@@ -7926,10 +7934,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7952,13 +7960,13 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>172</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7970,7 +7978,7 @@
         <v>84</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>84</v>
@@ -8018,7 +8026,7 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -8050,10 +8058,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -8076,13 +8084,13 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -8133,7 +8141,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -8174,13 +8182,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>84</v>
@@ -8202,13 +8210,13 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -8300,7 +8308,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>152</v>
@@ -8424,7 +8432,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>159</v>
@@ -8548,7 +8556,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>163</v>
@@ -8591,7 +8599,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>84</v>
@@ -8674,7 +8682,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>170</v>
@@ -8700,7 +8708,7 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>172</v>
@@ -8772,7 +8780,7 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>84</v>
@@ -8798,10 +8806,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8827,16 +8835,16 @@
         <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8885,7 +8893,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8926,10 +8934,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8952,16 +8960,16 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -9011,7 +9019,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -9026,36 +9034,36 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -9081,13 +9089,13 @@
         <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -9113,11 +9121,11 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -9135,7 +9143,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>93</v>
@@ -9150,25 +9158,25 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -9176,10 +9184,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9202,16 +9210,16 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -9237,13 +9245,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -9261,7 +9269,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -9285,13 +9293,13 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -9302,10 +9310,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9331,13 +9339,13 @@
         <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -9348,7 +9356,7 @@
         <v>84</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>84</v>
@@ -9363,13 +9371,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -9387,7 +9395,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>93</v>
@@ -9402,7 +9410,7 @@
         <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>84</v>
@@ -9411,16 +9419,16 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -9428,10 +9436,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9454,16 +9462,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -9474,7 +9482,7 @@
         <v>84</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>84</v>
@@ -9489,19 +9497,19 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -9511,7 +9519,7 @@
         <v>143</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9526,7 +9534,7 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>84</v>
@@ -9538,13 +9546,13 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -9552,13 +9560,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>84</v>
@@ -9580,16 +9588,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9615,13 +9623,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -9639,7 +9647,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9666,13 +9674,13 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9680,10 +9688,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9709,10 +9717,10 @@
         <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9739,13 +9747,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -9763,7 +9771,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9787,16 +9795,16 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9804,10 +9812,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9830,16 +9838,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9889,7 +9897,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9919,7 +9927,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9930,10 +9938,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9956,13 +9964,13 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -10013,7 +10021,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -10043,7 +10051,7 @@
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -10054,10 +10062,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -10080,16 +10088,16 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -10115,17 +10123,17 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -10135,7 +10143,7 @@
         <v>143</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>93</v>
@@ -10159,30 +10167,30 @@
         <v>84</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>84</v>
@@ -10204,16 +10212,16 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -10239,11 +10247,11 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -10261,7 +10269,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>93</v>
@@ -10285,27 +10293,27 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10426,10 +10434,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10552,10 +10560,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10581,16 +10589,16 @@
         <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10639,7 +10647,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10669,21 +10677,21 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10804,10 +10812,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10930,10 +10938,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10978,7 +10986,7 @@
         <v>84</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>84</v>
@@ -11032,7 +11040,7 @@
         <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>84</v>
@@ -11047,21 +11055,21 @@
         <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11087,13 +11095,13 @@
         <v>153</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -11143,7 +11151,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -11173,21 +11181,21 @@
         <v>84</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11213,14 +11221,14 @@
         <v>114</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -11269,7 +11277,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -11284,10 +11292,10 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>84</v>
@@ -11299,21 +11307,21 @@
         <v>84</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11339,14 +11347,14 @@
         <v>153</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -11395,7 +11403,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -11425,21 +11433,21 @@
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11462,19 +11470,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -11523,7 +11531,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11553,21 +11561,21 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11593,16 +11601,16 @@
         <v>153</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -11651,7 +11659,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11666,10 +11674,10 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>84</v>
@@ -11681,21 +11689,21 @@
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11718,16 +11726,16 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11777,7 +11785,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>93</v>
@@ -11792,36 +11800,36 @@
         <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11844,16 +11852,16 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11903,7 +11911,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11927,27 +11935,27 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11970,13 +11978,13 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -12027,7 +12035,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -12051,16 +12059,16 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>84</v>
@@ -12068,10 +12076,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12094,13 +12102,13 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -12151,7 +12159,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -12166,36 +12174,36 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12218,13 +12226,13 @@
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -12275,7 +12283,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -12290,25 +12298,25 @@
         <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>84</v>
@@ -12316,10 +12324,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12342,13 +12350,13 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -12399,7 +12407,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -12423,16 +12431,16 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>84</v>
@@ -12440,10 +12448,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12466,16 +12474,16 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12501,13 +12509,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -12525,7 +12533,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12549,13 +12557,13 @@
         <v>84</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12566,10 +12574,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12592,13 +12600,13 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -12649,7 +12657,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12679,10 +12687,10 @@
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>84</v>
@@ -12690,10 +12698,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12716,16 +12724,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12751,13 +12759,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12775,7 +12783,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12799,27 +12807,27 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12940,10 +12948,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13066,10 +13074,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13095,16 +13103,16 @@
         <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -13153,7 +13161,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -13183,21 +13191,21 @@
         <v>84</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13223,16 +13231,16 @@
         <v>153</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -13281,7 +13289,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -13296,10 +13304,10 @@
         <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>84</v>
@@ -13311,21 +13319,21 @@
         <v>84</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13348,16 +13356,16 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13407,7 +13415,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13431,16 +13439,16 @@
         <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>84</v>
@@ -13448,10 +13456,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13474,13 +13482,13 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13531,7 +13539,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13555,13 +13563,13 @@
         <v>84</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13572,10 +13580,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13601,10 +13609,10 @@
         <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -13655,7 +13663,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13685,7 +13693,7 @@
         <v>84</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13696,10 +13704,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13722,13 +13730,13 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -13779,7 +13787,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13803,13 +13811,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13820,10 +13828,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13846,17 +13854,17 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13905,7 +13913,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13929,13 +13937,13 @@
         <v>84</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13946,10 +13954,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13972,16 +13980,16 @@
         <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -14007,13 +14015,13 @@
         <v>84</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>84</v>
@@ -14031,7 +14039,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -14061,7 +14069,7 @@
         <v>84</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -14072,10 +14080,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14098,13 +14106,13 @@
         <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -14155,7 +14163,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -14179,13 +14187,13 @@
         <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -14196,10 +14204,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14222,13 +14230,13 @@
         <v>84</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -14279,7 +14287,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -14303,13 +14311,13 @@
         <v>84</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -14320,10 +14328,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14346,16 +14354,16 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -14405,7 +14413,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14429,13 +14437,13 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14446,10 +14454,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14570,10 +14578,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14696,14 +14704,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14725,16 +14733,16 @@
         <v>139</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14783,7 +14791,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14824,10 +14832,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14850,17 +14858,17 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14909,7 +14917,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14939,21 +14947,21 @@
         <v>84</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14979,14 +14987,14 @@
         <v>153</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -15035,7 +15043,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -15050,7 +15058,7 @@
         <v>106</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>84</v>
@@ -15065,21 +15073,21 @@
         <v>84</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15102,19 +15110,19 @@
         <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -15139,13 +15147,13 @@
         <v>84</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -15163,7 +15171,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -15193,21 +15201,21 @@
         <v>84</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15233,10 +15241,10 @@
         <v>153</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -15287,7 +15295,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -15302,10 +15310,10 @@
         <v>106</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>84</v>
@@ -15317,21 +15325,21 @@
         <v>84</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15354,19 +15362,19 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15415,7 +15423,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15445,7 +15453,7 @@
         <v>84</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -15456,10 +15464,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15482,16 +15490,16 @@
         <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -15517,13 +15525,13 @@
         <v>84</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -15541,7 +15549,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15571,21 +15579,21 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15608,19 +15616,19 @@
         <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
@@ -15645,13 +15653,13 @@
         <v>84</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>84</v>
@@ -15669,7 +15677,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15699,21 +15707,21 @@
         <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15736,17 +15744,17 @@
         <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
@@ -15771,13 +15779,13 @@
         <v>84</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15795,7 +15803,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15825,21 +15833,21 @@
         <v>84</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR100" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15960,10 +15968,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -16086,10 +16094,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16115,16 +16123,16 @@
         <v>171</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -16173,7 +16181,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -16203,21 +16211,21 @@
         <v>84</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16338,10 +16346,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16464,10 +16472,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16512,7 +16520,7 @@
         <v>84</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>84</v>
@@ -16566,7 +16574,7 @@
         <v>106</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>84</v>
@@ -16581,21 +16589,21 @@
         <v>84</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR106" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16621,13 +16629,13 @@
         <v>153</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -16677,7 +16685,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16707,21 +16715,21 @@
         <v>84</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR107" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16747,14 +16755,14 @@
         <v>114</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>84</v>
@@ -16803,7 +16811,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16818,10 +16826,10 @@
         <v>106</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>84</v>
@@ -16833,21 +16841,21 @@
         <v>84</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16873,14 +16881,14 @@
         <v>153</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
@@ -16929,7 +16937,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16959,21 +16967,21 @@
         <v>84</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16996,19 +17004,19 @@
         <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -17057,7 +17065,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -17087,21 +17095,21 @@
         <v>84</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17127,16 +17135,16 @@
         <v>153</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -17185,7 +17193,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -17215,21 +17223,21 @@
         <v>84</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR111" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17252,19 +17260,19 @@
         <v>94</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>84</v>
@@ -17289,13 +17297,13 @@
         <v>84</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>84</v>
@@ -17313,7 +17321,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -17343,21 +17351,21 @@
         <v>84</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR112" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17380,13 +17388,13 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -17437,7 +17445,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17473,15 +17481,15 @@
         <v>84</v>
       </c>
       <c r="AR113" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17602,10 +17610,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17728,13 +17736,13 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>84</v>
@@ -17756,16 +17764,16 @@
         <v>84</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -17856,10 +17864,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17980,10 +17988,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18104,10 +18112,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18147,7 +18155,7 @@
       </c>
       <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="S119" t="s" s="2">
         <v>84</v>
@@ -18230,10 +18238,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18256,13 +18264,13 @@
         <v>84</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>172</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -18322,16 +18330,16 @@
         <v>93</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>84</v>
@@ -18354,10 +18362,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18380,17 +18388,17 @@
         <v>94</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>84</v>
@@ -18415,13 +18423,13 @@
         <v>84</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>84</v>
@@ -18439,7 +18447,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18475,15 +18483,15 @@
         <v>84</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18506,19 +18514,19 @@
         <v>94</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
@@ -18555,7 +18563,7 @@
         <v>84</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
@@ -18565,7 +18573,7 @@
         <v>143</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18595,24 +18603,24 @@
         <v>84</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR122" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>84</v>
@@ -18634,19 +18642,19 @@
         <v>84</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>84</v>
@@ -18695,7 +18703,7 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>82</v>
@@ -18707,7 +18715,7 @@
         <v>150</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>84</v>
@@ -18725,21 +18733,21 @@
         <v>84</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR123" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18860,10 +18868,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18986,10 +18994,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19012,19 +19020,19 @@
         <v>94</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -19073,7 +19081,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -19088,10 +19096,10 @@
         <v>106</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>84</v>
@@ -19103,21 +19111,21 @@
         <v>84</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19143,20 +19151,20 @@
         <v>114</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q127" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="R127" t="s" s="2">
         <v>84</v>
@@ -19177,13 +19185,13 @@
         <v>84</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>84</v>
@@ -19201,7 +19209,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -19231,21 +19239,21 @@
         <v>84</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR127" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19271,14 +19279,14 @@
         <v>153</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
@@ -19327,7 +19335,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -19342,10 +19350,10 @@
         <v>106</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>84</v>
@@ -19357,21 +19365,21 @@
         <v>84</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR128" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19397,14 +19405,14 @@
         <v>108</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19453,7 +19461,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19462,7 +19470,7 @@
         <v>93</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>106</v>
@@ -19483,21 +19491,21 @@
         <v>84</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR129" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19523,16 +19531,16 @@
         <v>114</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
@@ -19581,7 +19589,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19611,21 +19619,21 @@
         <v>84</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR130" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19648,19 +19656,19 @@
         <v>94</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>84</v>
@@ -19709,7 +19717,7 @@
         <v>84</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>82</v>
@@ -19739,21 +19747,21 @@
         <v>84</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="AQ131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR131" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19776,19 +19784,19 @@
         <v>94</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
@@ -19837,7 +19845,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -19867,21 +19875,21 @@
         <v>84</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR132" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19904,19 +19912,19 @@
         <v>94</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
@@ -19965,7 +19973,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -19995,7 +20003,7 @@
         <v>84</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>84</v>
@@ -20006,10 +20014,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20032,17 +20040,17 @@
         <v>94</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -20091,7 +20099,7 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
@@ -20121,7 +20129,7 @@
         <v>84</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>84</v>
@@ -20132,10 +20140,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20158,13 +20166,13 @@
         <v>84</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -20215,7 +20223,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -20242,10 +20250,10 @@
         <v>84</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>84</v>
@@ -20256,10 +20264,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20380,10 +20388,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20506,14 +20514,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -20535,16 +20543,16 @@
         <v>139</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>84</v>
@@ -20593,7 +20601,7 @@
         <v>84</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>82</v>
@@ -20634,10 +20642,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20660,16 +20668,16 @@
         <v>84</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -20719,7 +20727,7 @@
         <v>84</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>82</v>
@@ -20749,7 +20757,7 @@
         <v>84</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="AQ139" t="s" s="2">
         <v>84</v>
@@ -20760,10 +20768,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20884,10 +20892,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21010,14 +21018,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -21039,16 +21047,16 @@
         <v>139</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>84</v>
@@ -21097,7 +21105,7 @@
         <v>84</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>82</v>
@@ -21138,10 +21146,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21164,13 +21172,13 @@
         <v>84</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -21221,7 +21229,7 @@
         <v>84</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>82</v>
@@ -21251,7 +21259,7 @@
         <v>84</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="AQ143" t="s" s="2">
         <v>84</v>
@@ -21262,10 +21270,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21288,13 +21296,13 @@
         <v>84</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -21345,7 +21353,7 @@
         <v>84</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>82</v>
@@ -21375,7 +21383,7 @@
         <v>84</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="AQ144" t="s" s="2">
         <v>84</v>
@@ -21386,10 +21394,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21412,13 +21420,13 @@
         <v>84</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -21469,7 +21477,7 @@
         <v>84</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>82</v>
@@ -21499,7 +21507,7 @@
         <v>84</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="AQ145" t="s" s="2">
         <v>84</v>
@@ -21510,10 +21518,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21536,19 +21544,19 @@
         <v>84</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>84</v>
@@ -21597,7 +21605,7 @@
         <v>84</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>82</v>
@@ -21624,10 +21632,10 @@
         <v>84</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="AQ146" t="s" s="2">
         <v>84</v>
@@ -21638,10 +21646,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21762,10 +21770,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21888,10 +21896,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21914,16 +21922,16 @@
         <v>94</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -21973,7 +21981,7 @@
         <v>84</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>82</v>
@@ -21982,7 +21990,7 @@
         <v>93</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>106</v>
@@ -22003,21 +22011,21 @@
         <v>84</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AQ149" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR149" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22040,23 +22048,23 @@
         <v>94</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q150" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="R150" t="s" s="2">
         <v>84</v>
@@ -22101,7 +22109,7 @@
         <v>84</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>82</v>
@@ -22110,13 +22118,13 @@
         <v>93</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>84</v>
@@ -22131,21 +22139,21 @@
         <v>84</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="AQ150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR150" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22168,16 +22176,16 @@
         <v>84</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -22227,7 +22235,7 @@
         <v>84</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>82</v>
@@ -22242,10 +22250,10 @@
         <v>106</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>84</v>
@@ -22254,24 +22262,24 @@
         <v>84</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="AQ151" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR151" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22294,13 +22302,13 @@
         <v>84</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -22351,7 +22359,7 @@
         <v>84</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>82</v>
@@ -22378,24 +22386,24 @@
         <v>84</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR152" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22516,10 +22524,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22642,10 +22650,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22668,19 +22676,19 @@
         <v>94</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>84</v>
@@ -22729,7 +22737,7 @@
         <v>84</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>82</v>
@@ -22744,13 +22752,13 @@
         <v>106</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>84</v>
@@ -22759,21 +22767,21 @@
         <v>84</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="AQ155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR155" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22799,20 +22807,20 @@
         <v>114</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q156" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="R156" t="s" s="2">
         <v>84</v>
@@ -22833,13 +22841,13 @@
         <v>84</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>84</v>
@@ -22857,7 +22865,7 @@
         <v>84</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>82</v>
@@ -22887,21 +22895,21 @@
         <v>84</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="AQ156" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR156" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22927,14 +22935,14 @@
         <v>153</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>84</v>
@@ -22983,7 +22991,7 @@
         <v>84</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>82</v>
@@ -23013,21 +23021,21 @@
         <v>84</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AQ157" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR157" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23053,14 +23061,14 @@
         <v>108</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>84</v>
@@ -23109,7 +23117,7 @@
         <v>84</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>82</v>
@@ -23118,7 +23126,7 @@
         <v>93</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>106</v>
@@ -23139,21 +23147,21 @@
         <v>84</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AQ158" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR158" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23179,16 +23187,16 @@
         <v>114</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>84</v>
@@ -23237,7 +23245,7 @@
         <v>84</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>82</v>
@@ -23267,21 +23275,21 @@
         <v>84</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="AQ159" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR159" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23304,16 +23312,16 @@
         <v>84</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -23363,7 +23371,7 @@
         <v>84</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
@@ -23378,22 +23386,22 @@
         <v>106</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="AQ160" t="s" s="2">
         <v>84</v>
@@ -23404,10 +23412,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23430,13 +23438,13 @@
         <v>84</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -23487,7 +23495,7 @@
         <v>84</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>82</v>
@@ -23517,10 +23525,10 @@
         <v>84</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AR161" t="s" s="2">
         <v>84</v>
@@ -23528,10 +23536,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23554,13 +23562,13 @@
         <v>84</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23611,7 +23619,7 @@
         <v>84</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23638,10 +23646,10 @@
         <v>84</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>84</v>
@@ -23652,10 +23660,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23776,10 +23784,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23902,14 +23910,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -23931,16 +23939,16 @@
         <v>139</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N165" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>84</v>
@@ -23989,7 +23997,7 @@
         <v>84</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>82</v>
@@ -24030,10 +24038,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24056,16 +24064,16 @@
         <v>84</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -24091,13 +24099,13 @@
         <v>84</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>84</v>
@@ -24115,7 +24123,7 @@
         <v>84</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>93</v>
@@ -24142,24 +24150,24 @@
         <v>84</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="AQ166" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR166" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24182,13 +24190,13 @@
         <v>84</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -24215,13 +24223,13 @@
         <v>84</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>84</v>
@@ -24239,7 +24247,7 @@
         <v>84</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>82</v>
@@ -24266,24 +24274,24 @@
         <v>84</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="AQ167" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR167" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24306,13 +24314,13 @@
         <v>84</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -24363,7 +24371,7 @@
         <v>84</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -24387,13 +24395,13 @@
         <v>84</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="AQ168" t="s" s="2">
         <v>84</v>
@@ -24404,14 +24412,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -24430,16 +24438,16 @@
         <v>84</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -24489,7 +24497,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>82</v>
@@ -24519,7 +24527,7 @@
         <v>84</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>84</v>
@@ -24530,10 +24538,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24556,16 +24564,16 @@
         <v>84</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -24615,7 +24623,7 @@
         <v>84</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>82</v>
@@ -24639,13 +24647,13 @@
         <v>84</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="AQ170" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -612,7 +612,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-MedicationRequestOutpatient-1746-1:if P then fixed value http://va.gov/terminology/vistaDefinedTerms/52-100 {null}</t>
+mro-27-1746-1:undefined: if P then http://va.gov/terminology/vistaDefinedTerms/52-100 {null}</t>
   </si>
   <si>
     <t>1746-1: fixed value = http://va.gov/terminology/vistaDefinedTerms/52-100 case P</t>
@@ -667,7 +667,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-MedicationRequestOutpatient-1746:if P then fixed value #active-parked {null}</t>
+mro-27-1746:52-11: if P then #active-parked {null}</t>
   </si>
   <si>
     <t>1746: fixed value = #active-parked when PRESCRIPTION - MAIL/WINDOW/PARK (52-11) case P</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="949">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,6 +676,9 @@
     <t>RxOut.RxOutpat.RxStatus</t>
   </si>
   <si>
+    <t>pharmacy.routing</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
@@ -775,6 +778,9 @@
     <t>RxOut.RxOutpat.CancelDate</t>
   </si>
   <si>
+    <t>pharmacy.stop</t>
+  </si>
+  <si>
     <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig</t>
   </si>
   <si>
@@ -969,6 +975,9 @@
     <t>RxOut.RxOutpat.RxNumber</t>
   </si>
   <si>
+    <t>pharmacy.prescription</t>
+  </si>
+  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -1003,6 +1012,9 @@
   </si>
   <si>
     <t>799: terminologyMaps using VF_OutMedRequestStatus on PRESCRIPTION - STATUS (52-100)</t>
+  </si>
+  <si>
+    <t>pharmacy.status,pharmacy.vaStatus</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -1326,6 +1338,9 @@
     <t>RxOut.RxOutpat.LocalDrugIEN,RxOut.RxOutpat.NationalDrugIEN,RxOut.RxOutpatFill.LocalDrugIEN,RxOut.RxOutpatFill.NationalDrugIEN</t>
   </si>
   <si>
+    <t>pharmacy.product [m]</t>
+  </si>
+  <si>
     <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.display</t>
   </si>
   <si>
@@ -1469,6 +1484,9 @@
     <t>RxOut.ActivityLog.IssueDateTime,RxOut.RxOutpat.IssueDate,RxOut.RxOutpatExt.IssueDateTime,RxOut.RxOutpatFill.IssueDate,RxOut.RxOutpatMedInstructions.IssueDate,RxOut.RxOutpatSig.IssueDate</t>
   </si>
   <si>
+    <t>pharmacy.start</t>
+  </si>
+  <si>
     <t>Request.authoredOn</t>
   </si>
   <si>
@@ -1503,6 +1521,9 @@
     <t>RxOut.RxOutpat.ProviderIEN</t>
   </si>
   <si>
+    <t>pharmacy.currentProvider,pharmacy.orderingProvider</t>
+  </si>
+  <si>
     <t>Request.requester</t>
   </si>
   <si>
@@ -1906,6 +1927,9 @@
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
   </si>
   <si>
+    <t>pharmacy.ptInstructions</t>
+  </si>
+  <si>
     <t>MedicationRequest.dosageInstruction.timing</t>
   </si>
   <si>
@@ -2053,6 +2077,9 @@
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.MedRoute</t>
+  </si>
+  <si>
+    <t>pharmacy.dose [m]</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.route.coding.display</t>
@@ -2672,6 +2699,9 @@
     <t>815: source value from PRESCRIPTION - EXPIRATION DATE (52-26)</t>
   </si>
   <si>
+    <t>pharmacy.expires</t>
+  </si>
+  <si>
     <t>./high</t>
   </si>
   <si>
@@ -2700,6 +2730,9 @@
     <t>RxOut.RxOutpat.MaxRefills</t>
   </si>
   <si>
+    <t>pharmacy.fillsAllowed</t>
+  </si>
+  <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Quantity</t>
   </si>
   <si>
@@ -2739,7 +2772,7 @@
     <t>1669: source value from PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
-    <t>Pharmacy: quantity</t>
+    <t>pharmacy.quantity</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.quantity.comparator</t>
@@ -2769,7 +2802,7 @@
     <t>1670: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
   </si>
   <si>
-    <t>Pharmacy: daysSupply</t>
+    <t>pharmacy.daysSupply</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Substitutions</t>
@@ -3284,7 +3317,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="175.39453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="50.88671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -5664,7 +5697,7 @@
         <v>211</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>84</v>
@@ -5673,21 +5706,21 @@
         <v>84</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5713,14 +5746,14 @@
         <v>153</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -5769,7 +5802,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5799,21 +5832,21 @@
         <v>84</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5836,19 +5869,19 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -5897,7 +5930,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5927,24 +5960,24 @@
         <v>84</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>84</v>
@@ -5966,13 +5999,13 @@
         <v>84</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -6064,7 +6097,7 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>152</v>
@@ -6188,7 +6221,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>159</v>
@@ -6312,7 +6345,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>163</v>
@@ -6355,7 +6388,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>84</v>
@@ -6438,7 +6471,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>170</v>
@@ -6464,7 +6497,7 @@
         <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>172</v>
@@ -6536,13 +6569,13 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>84</v>
@@ -6562,13 +6595,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>84</v>
@@ -6590,13 +6623,13 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6688,7 +6721,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>152</v>
@@ -6812,7 +6845,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>159</v>
@@ -6936,7 +6969,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>163</v>
@@ -6979,7 +7012,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>84</v>
@@ -7062,7 +7095,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>170</v>
@@ -7088,7 +7121,7 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>172</v>
@@ -7160,10 +7193,10 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>84</v>
@@ -7186,7 +7219,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>176</v>
@@ -7215,10 +7248,10 @@
         <v>153</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -7310,7 +7343,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>178</v>
@@ -7432,13 +7465,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -7460,16 +7493,16 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -7560,10 +7593,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7684,10 +7717,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7808,10 +7841,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7851,7 +7884,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>84</v>
@@ -7934,10 +7967,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7960,13 +7993,13 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>172</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7978,7 +8011,7 @@
         <v>84</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>84</v>
@@ -8026,7 +8059,7 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -8058,10 +8091,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -8084,13 +8117,13 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -8141,7 +8174,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -8182,13 +8215,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>84</v>
@@ -8210,13 +8243,13 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -8308,7 +8341,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>152</v>
@@ -8432,7 +8465,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>159</v>
@@ -8556,7 +8589,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>163</v>
@@ -8599,7 +8632,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>84</v>
@@ -8682,7 +8715,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>170</v>
@@ -8708,7 +8741,7 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>172</v>
@@ -8780,7 +8813,7 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>84</v>
@@ -8806,10 +8839,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8835,16 +8868,16 @@
         <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8893,7 +8926,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8934,10 +8967,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8960,16 +8993,16 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -9019,7 +9052,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -9034,36 +9067,36 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>84</v>
+        <v>308</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -9089,13 +9122,13 @@
         <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -9121,11 +9154,11 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -9143,7 +9176,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>93</v>
@@ -9158,25 +9191,25 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>211</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>84</v>
+        <v>321</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -9184,10 +9217,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9210,16 +9243,16 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -9245,13 +9278,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -9269,7 +9302,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -9293,13 +9326,13 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -9310,10 +9343,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9339,13 +9372,13 @@
         <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -9356,46 +9389,46 @@
         <v>84</v>
       </c>
       <c r="S49" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>93</v>
@@ -9410,7 +9443,7 @@
         <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>84</v>
@@ -9419,16 +9452,16 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -9436,10 +9469,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9462,16 +9495,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -9482,7 +9515,7 @@
         <v>84</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>84</v>
@@ -9497,19 +9530,19 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -9519,7 +9552,7 @@
         <v>143</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9534,7 +9567,7 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>84</v>
@@ -9546,13 +9579,13 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -9560,13 +9593,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>84</v>
@@ -9588,16 +9621,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9623,13 +9656,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -9647,7 +9680,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9674,13 +9707,13 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9688,10 +9721,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9717,10 +9750,10 @@
         <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9747,31 +9780,31 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Z52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9795,16 +9828,16 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9812,10 +9845,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9838,16 +9871,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9897,7 +9930,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9927,7 +9960,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9938,10 +9971,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9964,13 +9997,13 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -10021,7 +10054,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -10051,7 +10084,7 @@
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -10062,10 +10095,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -10088,16 +10121,16 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -10123,17 +10156,17 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -10143,7 +10176,7 @@
         <v>143</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>93</v>
@@ -10167,30 +10200,30 @@
         <v>84</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>84</v>
@@ -10212,16 +10245,16 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -10247,11 +10280,11 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -10269,7 +10302,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>93</v>
@@ -10293,27 +10326,27 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10434,10 +10467,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10560,10 +10593,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10589,16 +10622,16 @@
         <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10647,7 +10680,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10677,21 +10710,21 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10812,10 +10845,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10938,10 +10971,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10986,7 +11019,7 @@
         <v>84</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>84</v>
@@ -11040,7 +11073,7 @@
         <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>84</v>
@@ -11066,10 +11099,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11192,10 +11225,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11292,13 +11325,13 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>84</v>
+        <v>421</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>84</v>
@@ -11307,21 +11340,21 @@
         <v>84</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11347,14 +11380,14 @@
         <v>153</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -11403,7 +11436,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -11433,21 +11466,21 @@
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11470,19 +11503,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -11531,7 +11564,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11561,21 +11594,21 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11601,16 +11634,16 @@
         <v>153</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -11659,7 +11692,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11674,13 +11707,13 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>84</v>
+        <v>421</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>84</v>
@@ -11689,21 +11722,21 @@
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11726,16 +11759,16 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11785,7 +11818,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>93</v>
@@ -11800,36 +11833,36 @@
         <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11852,16 +11885,16 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11911,7 +11944,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11935,27 +11968,27 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11978,13 +12011,13 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -12035,7 +12068,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -12059,16 +12092,16 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>84</v>
@@ -12076,10 +12109,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12102,13 +12135,13 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -12159,7 +12192,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -12174,36 +12207,36 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12226,13 +12259,13 @@
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -12283,7 +12316,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -12298,25 +12331,25 @@
         <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>84</v>
+        <v>480</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>84</v>
@@ -12324,10 +12357,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12350,13 +12383,13 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -12407,7 +12440,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -12431,16 +12464,16 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>84</v>
@@ -12448,10 +12481,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12474,16 +12507,16 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12509,13 +12542,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -12533,7 +12566,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12557,13 +12590,13 @@
         <v>84</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12574,10 +12607,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12600,13 +12633,13 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -12657,7 +12690,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12687,10 +12720,10 @@
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>84</v>
@@ -12698,10 +12731,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12724,16 +12757,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12759,13 +12792,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12783,7 +12816,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12807,27 +12840,27 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12948,10 +12981,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13074,10 +13107,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13103,16 +13136,16 @@
         <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -13161,7 +13194,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -13191,21 +13224,21 @@
         <v>84</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13231,16 +13264,16 @@
         <v>153</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -13289,7 +13322,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -13304,10 +13337,10 @@
         <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>84</v>
@@ -13319,21 +13352,21 @@
         <v>84</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13356,16 +13389,16 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13415,7 +13448,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13439,16 +13472,16 @@
         <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>84</v>
@@ -13456,10 +13489,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13482,13 +13515,13 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13539,7 +13572,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13563,13 +13596,13 @@
         <v>84</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13580,10 +13613,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13609,10 +13642,10 @@
         <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -13663,7 +13696,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13693,7 +13726,7 @@
         <v>84</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13704,10 +13737,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13730,13 +13763,13 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -13787,7 +13820,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13811,13 +13844,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13828,10 +13861,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13854,17 +13887,17 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13913,7 +13946,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13937,13 +13970,13 @@
         <v>84</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13954,10 +13987,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13980,16 +14013,16 @@
         <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -14015,13 +14048,13 @@
         <v>84</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>84</v>
@@ -14039,7 +14072,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -14069,7 +14102,7 @@
         <v>84</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -14080,10 +14113,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14106,13 +14139,13 @@
         <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -14163,7 +14196,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -14187,13 +14220,13 @@
         <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -14204,10 +14237,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14230,13 +14263,13 @@
         <v>84</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -14287,7 +14320,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -14311,13 +14344,13 @@
         <v>84</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -14328,10 +14361,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14354,16 +14387,16 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -14413,7 +14446,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14437,13 +14470,13 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14454,10 +14487,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14578,10 +14611,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14704,14 +14737,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14733,16 +14766,16 @@
         <v>139</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14791,7 +14824,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14832,10 +14865,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14858,17 +14891,17 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14917,7 +14950,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14947,21 +14980,21 @@
         <v>84</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14987,14 +15020,14 @@
         <v>153</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -15043,7 +15076,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -15058,36 +15091,36 @@
         <v>106</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP94" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AL94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>581</v>
-      </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>589</v>
+        <v>596</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15110,19 +15143,19 @@
         <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -15147,13 +15180,13 @@
         <v>84</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -15171,7 +15204,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -15201,21 +15234,21 @@
         <v>84</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15241,10 +15274,10 @@
         <v>153</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -15295,7 +15328,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -15310,13 +15343,13 @@
         <v>106</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>84</v>
+        <v>612</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>84</v>
@@ -15325,21 +15358,21 @@
         <v>84</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15362,19 +15395,19 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15423,7 +15456,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15453,7 +15486,7 @@
         <v>84</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -15464,10 +15497,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15490,16 +15523,16 @@
         <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -15525,13 +15558,13 @@
         <v>84</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -15549,7 +15582,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15579,21 +15612,21 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15616,19 +15649,19 @@
         <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
@@ -15653,13 +15686,13 @@
         <v>84</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>84</v>
@@ -15677,7 +15710,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15707,21 +15740,21 @@
         <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>632</v>
+        <v>640</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15744,17 +15777,17 @@
         <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
@@ -15779,13 +15812,13 @@
         <v>84</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15803,7 +15836,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15833,21 +15866,21 @@
         <v>84</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR100" t="s" s="2">
-        <v>641</v>
+        <v>649</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15968,10 +16001,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -16094,10 +16127,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16123,16 +16156,16 @@
         <v>171</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -16181,7 +16214,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -16211,21 +16244,21 @@
         <v>84</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16346,10 +16379,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16472,10 +16505,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16520,7 +16553,7 @@
         <v>84</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>84</v>
@@ -16574,7 +16607,7 @@
         <v>106</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>84</v>
@@ -16600,10 +16633,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16726,10 +16759,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16826,13 +16859,13 @@
         <v>106</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>84</v>
+        <v>662</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>84</v>
@@ -16841,21 +16874,21 @@
         <v>84</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16881,14 +16914,14 @@
         <v>153</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
@@ -16937,7 +16970,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16967,21 +17000,21 @@
         <v>84</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17004,19 +17037,19 @@
         <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -17065,7 +17098,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -17095,21 +17128,21 @@
         <v>84</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17135,16 +17168,16 @@
         <v>153</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -17193,7 +17226,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -17223,21 +17256,21 @@
         <v>84</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR111" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17260,19 +17293,19 @@
         <v>94</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>84</v>
@@ -17297,13 +17330,13 @@
         <v>84</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>84</v>
@@ -17321,7 +17354,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -17351,21 +17384,21 @@
         <v>84</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR112" t="s" s="2">
-        <v>666</v>
+        <v>675</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17388,13 +17421,13 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -17445,7 +17478,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17481,15 +17514,15 @@
         <v>84</v>
       </c>
       <c r="AR113" t="s" s="2">
-        <v>672</v>
+        <v>681</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17610,10 +17643,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17736,13 +17769,13 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>84</v>
@@ -17764,16 +17797,16 @@
         <v>84</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -17864,10 +17897,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17988,10 +18021,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>684</v>
+        <v>693</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18112,10 +18145,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18155,7 +18188,7 @@
       </c>
       <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="S119" t="s" s="2">
         <v>84</v>
@@ -18238,10 +18271,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>689</v>
+        <v>698</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18264,13 +18297,13 @@
         <v>84</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>172</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -18330,19 +18363,19 @@
         <v>93</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>84</v>
+        <v>662</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>84</v>
@@ -18362,10 +18395,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>693</v>
+        <v>702</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>693</v>
+        <v>702</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18388,17 +18421,17 @@
         <v>94</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>84</v>
@@ -18423,13 +18456,13 @@
         <v>84</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>84</v>
@@ -18447,7 +18480,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18483,15 +18516,15 @@
         <v>84</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>700</v>
+        <v>709</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18514,19 +18547,19 @@
         <v>94</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>706</v>
+        <v>715</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
@@ -18563,7 +18596,7 @@
         <v>84</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
@@ -18573,7 +18606,7 @@
         <v>143</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>707</v>
+        <v>716</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18603,24 +18636,24 @@
         <v>84</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR122" t="s" s="2">
-        <v>708</v>
+        <v>717</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>84</v>
@@ -18642,19 +18675,19 @@
         <v>84</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>712</v>
+        <v>721</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>714</v>
+        <v>723</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>706</v>
+        <v>715</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>84</v>
@@ -18703,7 +18736,7 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>707</v>
+        <v>716</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>82</v>
@@ -18715,7 +18748,7 @@
         <v>150</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>84</v>
@@ -18733,21 +18766,21 @@
         <v>84</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR123" t="s" s="2">
-        <v>717</v>
+        <v>726</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18868,10 +18901,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18994,10 +19027,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19020,19 +19053,19 @@
         <v>94</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>724</v>
+        <v>733</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>725</v>
+        <v>734</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>726</v>
+        <v>735</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -19081,7 +19114,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>729</v>
+        <v>738</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -19096,13 +19129,13 @@
         <v>106</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>84</v>
+        <v>662</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>84</v>
@@ -19111,21 +19144,21 @@
         <v>84</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>732</v>
+        <v>741</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>734</v>
+        <v>743</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19151,20 +19184,20 @@
         <v>114</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q127" t="s" s="2">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="R127" t="s" s="2">
         <v>84</v>
@@ -19185,13 +19218,13 @@
         <v>84</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>739</v>
+        <v>748</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>84</v>
@@ -19209,7 +19242,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>741</v>
+        <v>750</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -19239,21 +19272,21 @@
         <v>84</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>742</v>
+        <v>751</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR127" t="s" s="2">
-        <v>743</v>
+        <v>752</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19279,14 +19312,14 @@
         <v>153</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>747</v>
+        <v>756</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
@@ -19335,7 +19368,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -19350,13 +19383,13 @@
         <v>106</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>84</v>
+        <v>662</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>84</v>
@@ -19365,21 +19398,21 @@
         <v>84</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR128" t="s" s="2">
-        <v>753</v>
+        <v>762</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19405,14 +19438,14 @@
         <v>108</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19461,7 +19494,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19470,7 +19503,7 @@
         <v>93</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>106</v>
@@ -19491,21 +19524,21 @@
         <v>84</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR129" t="s" s="2">
-        <v>753</v>
+        <v>762</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>763</v>
+        <v>772</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19531,16 +19564,16 @@
         <v>114</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
@@ -19589,7 +19622,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19619,21 +19652,21 @@
         <v>84</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR130" t="s" s="2">
-        <v>753</v>
+        <v>762</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19656,19 +19689,19 @@
         <v>94</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>771</v>
+        <v>780</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>772</v>
+        <v>781</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>774</v>
+        <v>783</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>84</v>
@@ -19717,7 +19750,7 @@
         <v>84</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>776</v>
+        <v>785</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>82</v>
@@ -19747,21 +19780,21 @@
         <v>84</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="AQ131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR131" t="s" s="2">
-        <v>778</v>
+        <v>787</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19784,19 +19817,19 @@
         <v>94</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>782</v>
+        <v>791</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
@@ -19845,7 +19878,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>785</v>
+        <v>794</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -19875,21 +19908,21 @@
         <v>84</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>786</v>
+        <v>795</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR132" t="s" s="2">
-        <v>787</v>
+        <v>796</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19912,19 +19945,19 @@
         <v>94</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>789</v>
+        <v>798</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>791</v>
+        <v>800</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>792</v>
+        <v>801</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
@@ -19973,7 +20006,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -20003,7 +20036,7 @@
         <v>84</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>84</v>
@@ -20014,10 +20047,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20040,17 +20073,17 @@
         <v>94</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>796</v>
+        <v>805</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>798</v>
+        <v>807</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -20099,7 +20132,7 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>799</v>
+        <v>808</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
@@ -20129,7 +20162,7 @@
         <v>84</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>84</v>
@@ -20140,10 +20173,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>800</v>
+        <v>809</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>800</v>
+        <v>809</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20166,13 +20199,13 @@
         <v>84</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>801</v>
+        <v>810</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>803</v>
+        <v>812</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -20223,7 +20256,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>800</v>
+        <v>809</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -20250,10 +20283,10 @@
         <v>84</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>804</v>
+        <v>813</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>84</v>
@@ -20264,10 +20297,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>806</v>
+        <v>815</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>806</v>
+        <v>815</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20388,10 +20421,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>807</v>
+        <v>816</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>807</v>
+        <v>816</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20514,14 +20547,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>808</v>
+        <v>817</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>808</v>
+        <v>817</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -20543,16 +20576,16 @@
         <v>139</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>84</v>
@@ -20601,7 +20634,7 @@
         <v>84</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>82</v>
@@ -20642,10 +20675,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>809</v>
+        <v>818</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>809</v>
+        <v>818</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20668,16 +20701,16 @@
         <v>84</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>801</v>
+        <v>810</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>812</v>
+        <v>821</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -20727,7 +20760,7 @@
         <v>84</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>809</v>
+        <v>818</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>82</v>
@@ -20757,7 +20790,7 @@
         <v>84</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="AQ139" t="s" s="2">
         <v>84</v>
@@ -20768,10 +20801,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20892,10 +20925,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21018,14 +21051,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>816</v>
+        <v>825</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>816</v>
+        <v>825</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -21047,16 +21080,16 @@
         <v>139</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>84</v>
@@ -21105,7 +21138,7 @@
         <v>84</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>82</v>
@@ -21146,10 +21179,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21172,13 +21205,13 @@
         <v>84</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>818</v>
+        <v>827</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>819</v>
+        <v>828</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -21229,7 +21262,7 @@
         <v>84</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>82</v>
@@ -21259,7 +21292,7 @@
         <v>84</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>820</v>
+        <v>829</v>
       </c>
       <c r="AQ143" t="s" s="2">
         <v>84</v>
@@ -21270,10 +21303,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>821</v>
+        <v>830</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>821</v>
+        <v>830</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21296,13 +21329,13 @@
         <v>84</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>822</v>
+        <v>831</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>823</v>
+        <v>832</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>824</v>
+        <v>833</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -21353,7 +21386,7 @@
         <v>84</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>821</v>
+        <v>830</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>82</v>
@@ -21383,7 +21416,7 @@
         <v>84</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>825</v>
+        <v>834</v>
       </c>
       <c r="AQ144" t="s" s="2">
         <v>84</v>
@@ -21394,10 +21427,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>826</v>
+        <v>835</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>826</v>
+        <v>835</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21420,13 +21453,13 @@
         <v>84</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>822</v>
+        <v>831</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>827</v>
+        <v>836</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>828</v>
+        <v>837</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -21477,7 +21510,7 @@
         <v>84</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>826</v>
+        <v>835</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>82</v>
@@ -21507,7 +21540,7 @@
         <v>84</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>825</v>
+        <v>834</v>
       </c>
       <c r="AQ145" t="s" s="2">
         <v>84</v>
@@ -21518,10 +21551,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>829</v>
+        <v>838</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>829</v>
+        <v>838</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21544,19 +21577,19 @@
         <v>84</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>830</v>
+        <v>839</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>833</v>
+        <v>842</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>84</v>
@@ -21605,7 +21638,7 @@
         <v>84</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>829</v>
+        <v>838</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>82</v>
@@ -21632,10 +21665,10 @@
         <v>84</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>835</v>
+        <v>844</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>836</v>
+        <v>845</v>
       </c>
       <c r="AQ146" t="s" s="2">
         <v>84</v>
@@ -21646,10 +21679,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>837</v>
+        <v>846</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>837</v>
+        <v>846</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21770,10 +21803,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21896,10 +21929,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21922,16 +21955,16 @@
         <v>94</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>840</v>
+        <v>849</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>841</v>
+        <v>850</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>842</v>
+        <v>851</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -21981,7 +22014,7 @@
         <v>84</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>82</v>
@@ -21990,7 +22023,7 @@
         <v>93</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>106</v>
@@ -22011,21 +22044,21 @@
         <v>84</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>845</v>
+        <v>854</v>
       </c>
       <c r="AQ149" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR149" t="s" s="2">
-        <v>846</v>
+        <v>855</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>847</v>
+        <v>856</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>847</v>
+        <v>856</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22048,23 +22081,23 @@
         <v>94</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>848</v>
+        <v>857</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q150" t="s" s="2">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="R150" t="s" s="2">
         <v>84</v>
@@ -22109,7 +22142,7 @@
         <v>84</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>82</v>
@@ -22118,19 +22151,19 @@
         <v>93</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>84</v>
+        <v>863</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>84</v>
@@ -22139,21 +22172,21 @@
         <v>84</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>854</v>
+        <v>864</v>
       </c>
       <c r="AQ150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR150" t="s" s="2">
-        <v>855</v>
+        <v>865</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22176,16 +22209,16 @@
         <v>84</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>858</v>
+        <v>868</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>859</v>
+        <v>869</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -22235,7 +22268,7 @@
         <v>84</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>82</v>
@@ -22250,36 +22283,36 @@
         <v>106</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>861</v>
+        <v>871</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>84</v>
+        <v>873</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="AQ151" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR151" t="s" s="2">
-        <v>865</v>
+        <v>876</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>866</v>
+        <v>877</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>866</v>
+        <v>877</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22302,13 +22335,13 @@
         <v>84</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>867</v>
+        <v>878</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>868</v>
+        <v>879</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -22359,7 +22392,7 @@
         <v>84</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>866</v>
+        <v>877</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>82</v>
@@ -22386,24 +22419,24 @@
         <v>84</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>870</v>
+        <v>881</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR152" t="s" s="2">
-        <v>871</v>
+        <v>882</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>872</v>
+        <v>883</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>872</v>
+        <v>883</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22524,10 +22557,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>873</v>
+        <v>884</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>873</v>
+        <v>884</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22650,10 +22683,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>874</v>
+        <v>885</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>874</v>
+        <v>885</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22676,19 +22709,19 @@
         <v>94</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>724</v>
+        <v>733</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>725</v>
+        <v>734</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>726</v>
+        <v>735</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>84</v>
@@ -22737,7 +22770,7 @@
         <v>84</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>729</v>
+        <v>738</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>82</v>
@@ -22752,13 +22785,13 @@
         <v>106</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>875</v>
+        <v>886</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>84</v>
@@ -22767,21 +22800,21 @@
         <v>84</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="AQ155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR155" t="s" s="2">
-        <v>732</v>
+        <v>741</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22807,20 +22840,20 @@
         <v>114</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q156" t="s" s="2">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="R156" t="s" s="2">
         <v>84</v>
@@ -22841,13 +22874,13 @@
         <v>84</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>739</v>
+        <v>748</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>84</v>
@@ -22865,7 +22898,7 @@
         <v>84</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>741</v>
+        <v>750</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>82</v>
@@ -22895,21 +22928,21 @@
         <v>84</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>742</v>
+        <v>751</v>
       </c>
       <c r="AQ156" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR156" t="s" s="2">
-        <v>743</v>
+        <v>752</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>878</v>
+        <v>889</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>878</v>
+        <v>889</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22935,14 +22968,14 @@
         <v>153</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>747</v>
+        <v>756</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>84</v>
@@ -22991,7 +23024,7 @@
         <v>84</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>82</v>
@@ -23021,21 +23054,21 @@
         <v>84</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="AQ157" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR157" t="s" s="2">
-        <v>753</v>
+        <v>762</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23061,14 +23094,14 @@
         <v>108</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>84</v>
@@ -23117,7 +23150,7 @@
         <v>84</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>82</v>
@@ -23126,7 +23159,7 @@
         <v>93</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>106</v>
@@ -23147,21 +23180,21 @@
         <v>84</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="AQ158" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR158" t="s" s="2">
-        <v>753</v>
+        <v>762</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>880</v>
+        <v>891</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>880</v>
+        <v>891</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23187,16 +23220,16 @@
         <v>114</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>84</v>
@@ -23245,7 +23278,7 @@
         <v>84</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>82</v>
@@ -23275,21 +23308,21 @@
         <v>84</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="AQ159" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR159" t="s" s="2">
-        <v>753</v>
+        <v>762</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>881</v>
+        <v>892</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>881</v>
+        <v>892</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23312,16 +23345,16 @@
         <v>84</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>822</v>
+        <v>831</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>882</v>
+        <v>893</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>883</v>
+        <v>894</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>884</v>
+        <v>895</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -23371,7 +23404,7 @@
         <v>84</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>881</v>
+        <v>892</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
@@ -23386,22 +23419,22 @@
         <v>106</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>885</v>
+        <v>896</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>887</v>
+        <v>898</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="AQ160" t="s" s="2">
         <v>84</v>
@@ -23412,10 +23445,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>889</v>
+        <v>900</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>889</v>
+        <v>900</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23438,13 +23471,13 @@
         <v>84</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>890</v>
+        <v>901</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>891</v>
+        <v>902</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>892</v>
+        <v>903</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -23495,7 +23528,7 @@
         <v>84</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>889</v>
+        <v>900</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>82</v>
@@ -23525,10 +23558,10 @@
         <v>84</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>893</v>
+        <v>904</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="AR161" t="s" s="2">
         <v>84</v>
@@ -23536,10 +23569,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23562,13 +23595,13 @@
         <v>84</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>801</v>
+        <v>810</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>895</v>
+        <v>906</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>896</v>
+        <v>907</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23619,7 +23652,7 @@
         <v>84</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23646,10 +23679,10 @@
         <v>84</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>84</v>
@@ -23660,10 +23693,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23784,10 +23817,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23910,14 +23943,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -23939,16 +23972,16 @@
         <v>139</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="N165" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>84</v>
@@ -23997,7 +24030,7 @@
         <v>84</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>82</v>
@@ -24038,10 +24071,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24064,16 +24097,16 @@
         <v>84</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -24099,13 +24132,13 @@
         <v>84</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>906</v>
+        <v>917</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>84</v>
@@ -24123,7 +24156,7 @@
         <v>84</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>93</v>
@@ -24150,24 +24183,24 @@
         <v>84</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="AQ166" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR166" t="s" s="2">
-        <v>909</v>
+        <v>920</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24190,13 +24223,13 @@
         <v>84</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>911</v>
+        <v>922</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>912</v>
+        <v>923</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -24223,13 +24256,13 @@
         <v>84</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>913</v>
+        <v>924</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>84</v>
@@ -24247,7 +24280,7 @@
         <v>84</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>82</v>
@@ -24274,24 +24307,24 @@
         <v>84</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>915</v>
+        <v>926</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>916</v>
+        <v>927</v>
       </c>
       <c r="AQ167" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR167" t="s" s="2">
-        <v>917</v>
+        <v>928</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24314,13 +24347,13 @@
         <v>84</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>919</v>
+        <v>930</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>921</v>
+        <v>932</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -24371,7 +24404,7 @@
         <v>84</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -24395,13 +24428,13 @@
         <v>84</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>922</v>
+        <v>933</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>915</v>
+        <v>926</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>923</v>
+        <v>934</v>
       </c>
       <c r="AQ168" t="s" s="2">
         <v>84</v>
@@ -24412,14 +24445,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>924</v>
+        <v>935</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>924</v>
+        <v>935</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>925</v>
+        <v>936</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -24438,16 +24471,16 @@
         <v>84</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>926</v>
+        <v>937</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>928</v>
+        <v>939</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -24497,7 +24530,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>924</v>
+        <v>935</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>82</v>
@@ -24527,7 +24560,7 @@
         <v>84</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>930</v>
+        <v>941</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>84</v>
@@ -24538,10 +24571,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24564,16 +24597,16 @@
         <v>84</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>932</v>
+        <v>943</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>933</v>
+        <v>944</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>934</v>
+        <v>945</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>935</v>
+        <v>946</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -24623,7 +24656,7 @@
         <v>84</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>82</v>
@@ -24647,13 +24680,13 @@
         <v>84</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>936</v>
+        <v>947</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>937</v>
+        <v>948</v>
       </c>
       <c r="AQ170" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="945">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,9 +676,6 @@
     <t>RxOut.RxOutpat.RxStatus</t>
   </si>
   <si>
-    <t>pharmacy.routing</t>
-  </si>
-  <si>
     <t>./code</t>
   </si>
   <si>
@@ -778,9 +775,6 @@
     <t>RxOut.RxOutpat.CancelDate</t>
   </si>
   <si>
-    <t>pharmacy.stop</t>
-  </si>
-  <si>
     <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig</t>
   </si>
   <si>
@@ -975,7 +969,7 @@
     <t>RxOut.RxOutpat.RxNumber</t>
   </si>
   <si>
-    <t>pharmacy.prescription</t>
+    <t>pharmacy (med).dose,med.dose</t>
   </si>
   <si>
     <t>Request.identifier</t>
@@ -1012,9 +1006,6 @@
   </si>
   <si>
     <t>799: terminologyMaps using VF_OutMedRequestStatus on PRESCRIPTION - STATUS (52-100)</t>
-  </si>
-  <si>
-    <t>pharmacy.status,pharmacy.vaStatus</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -1338,7 +1329,7 @@
     <t>RxOut.RxOutpat.LocalDrugIEN,RxOut.RxOutpat.NationalDrugIEN,RxOut.RxOutpatFill.LocalDrugIEN,RxOut.RxOutpatFill.NationalDrugIEN</t>
   </si>
   <si>
-    <t>pharmacy.product [m]</t>
+    <t>pharmacy (med).route,med.route</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.display</t>
@@ -1403,6 +1394,9 @@
   </si>
   <si>
     <t>RxOut.ActivityLog.PatientIEN,RxOut.ActivityLogOtherComments.PatientIEN,RxOut.RxOutpat.PatientIEN,RxOut.RxOutpatExt.PatientIEN,RxOut.RxOutpatExt.PatientSID,RxOut.RxOutpatFill.PatientIEN,RxOut.RxOutpatMedInstructions.PatientIEN,RxOut.RxOutpatSig.PatientIEN</t>
+  </si>
+  <si>
+    <t>pharmacy (med).units,med.units</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -1484,7 +1478,7 @@
     <t>RxOut.ActivityLog.IssueDateTime,RxOut.RxOutpat.IssueDate,RxOut.RxOutpatExt.IssueDateTime,RxOut.RxOutpatFill.IssueDate,RxOut.RxOutpatMedInstructions.IssueDate,RxOut.RxOutpatSig.IssueDate</t>
   </si>
   <si>
-    <t>pharmacy.start</t>
+    <t>pharmacy (med).unitsPerDose,med.unitsPerDose</t>
   </si>
   <si>
     <t>Request.authoredOn</t>
@@ -1521,7 +1515,7 @@
     <t>RxOut.RxOutpat.ProviderIEN</t>
   </si>
   <si>
-    <t>pharmacy.currentProvider,pharmacy.orderingProvider</t>
+    <t>pharmacy (med).currentProvider,pharmacy (med).doseStart,pharmacy (med).doseStop,pharmacy (med).duration,med.currentProvider,med.doseStart,med.doseStop,med.duration</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -1927,9 +1921,6 @@
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
   </si>
   <si>
-    <t>pharmacy.ptInstructions</t>
-  </si>
-  <si>
     <t>MedicationRequest.dosageInstruction.timing</t>
   </si>
   <si>
@@ -2079,7 +2070,7 @@
     <t>RxOut.RxOutpatMedInstructions.MedRoute</t>
   </si>
   <si>
-    <t>pharmacy.dose [m]</t>
+    <t>pharmacy (med).dose [m],med.dose [m]</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.route.coding.display</t>
@@ -2699,7 +2690,7 @@
     <t>815: source value from PRESCRIPTION - EXPIRATION DATE (52-26)</t>
   </si>
   <si>
-    <t>pharmacy.expires</t>
+    <t>pharmacy (med).expires,med.expires</t>
   </si>
   <si>
     <t>./high</t>
@@ -2730,9 +2721,6 @@
     <t>RxOut.RxOutpat.MaxRefills</t>
   </si>
   <si>
-    <t>pharmacy.fillsAllowed</t>
-  </si>
-  <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Quantity</t>
   </si>
   <si>
@@ -2772,7 +2760,7 @@
     <t>1669: source value from PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
-    <t>pharmacy.quantity</t>
+    <t>pharmacy (med).schedule,med.schedule</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.quantity.comparator</t>
@@ -2802,7 +2790,7 @@
     <t>1670: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
   </si>
   <si>
-    <t>pharmacy.daysSupply</t>
+    <t>pharmacy (med).daysSupply,med.daysSupply</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Substitutions</t>
@@ -3317,7 +3305,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="175.39453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="50.88671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="166.08984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -5697,30 +5685,30 @@
         <v>211</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AN19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP19" t="s" s="2">
+      <c r="AQ19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR19" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR19" t="s" s="2">
-        <v>214</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5746,14 +5734,14 @@
         <v>153</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -5802,7 +5790,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5832,21 +5820,21 @@
         <v>84</v>
       </c>
       <c r="AP20" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR20" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR20" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5869,19 +5857,19 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -5930,7 +5918,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5960,24 +5948,24 @@
         <v>84</v>
       </c>
       <c r="AP21" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR21" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR21" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>84</v>
@@ -5999,13 +5987,13 @@
         <v>84</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -6097,7 +6085,7 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>152</v>
@@ -6221,7 +6209,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>159</v>
@@ -6345,7 +6333,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>163</v>
@@ -6388,7 +6376,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>84</v>
@@ -6471,7 +6459,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>170</v>
@@ -6497,7 +6485,7 @@
         <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>172</v>
@@ -6569,13 +6557,13 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>244</v>
-      </c>
       <c r="AM26" t="s" s="2">
-        <v>245</v>
+        <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>84</v>
@@ -6595,13 +6583,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>84</v>
@@ -6623,13 +6611,13 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6721,7 +6709,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>152</v>
@@ -6845,7 +6833,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>159</v>
@@ -6969,7 +6957,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>163</v>
@@ -7012,7 +7000,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>84</v>
@@ -7095,7 +7083,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>170</v>
@@ -7121,7 +7109,7 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>172</v>
@@ -7193,10 +7181,10 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>84</v>
@@ -7219,7 +7207,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>176</v>
@@ -7248,10 +7236,10 @@
         <v>153</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -7343,7 +7331,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>178</v>
@@ -7465,13 +7453,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -7493,16 +7481,16 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -7593,10 +7581,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7717,10 +7705,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7841,10 +7829,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7884,7 +7872,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>84</v>
@@ -7967,10 +7955,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7993,13 +7981,13 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>172</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -8011,7 +7999,7 @@
         <v>84</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>84</v>
@@ -8059,7 +8047,7 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -8091,10 +8079,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -8117,13 +8105,13 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -8174,7 +8162,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -8215,13 +8203,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>84</v>
@@ -8243,13 +8231,13 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -8341,7 +8329,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>152</v>
@@ -8465,7 +8453,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>159</v>
@@ -8589,7 +8577,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>163</v>
@@ -8632,7 +8620,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>84</v>
@@ -8715,7 +8703,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>170</v>
@@ -8741,7 +8729,7 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>172</v>
@@ -8813,7 +8801,7 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>84</v>
@@ -8839,10 +8827,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8868,16 +8856,16 @@
         <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8926,7 +8914,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8967,10 +8955,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8993,16 +8981,16 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -9052,7 +9040,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -9067,36 +9055,36 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AR46" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -9122,13 +9110,13 @@
         <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -9154,11 +9142,11 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -9176,7 +9164,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>93</v>
@@ -9191,25 +9179,25 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>211</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -9217,10 +9205,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9243,16 +9231,16 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -9278,13 +9266,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -9302,7 +9290,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -9326,13 +9314,13 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -9343,10 +9331,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9372,13 +9360,13 @@
         <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -9389,7 +9377,7 @@
         <v>84</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>84</v>
@@ -9404,13 +9392,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -9428,7 +9416,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>93</v>
@@ -9443,25 +9431,25 @@
         <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -9469,10 +9457,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9495,16 +9483,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -9515,34 +9503,34 @@
         <v>84</v>
       </c>
       <c r="S50" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB50" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -9552,7 +9540,7 @@
         <v>143</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9567,7 +9555,7 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>84</v>
@@ -9579,13 +9567,13 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -9593,13 +9581,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>84</v>
@@ -9621,16 +9609,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9656,13 +9644,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -9680,7 +9668,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9707,13 +9695,13 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9721,10 +9709,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9750,10 +9738,10 @@
         <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9780,13 +9768,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -9804,7 +9792,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9828,16 +9816,16 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9845,10 +9833,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9871,16 +9859,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9930,7 +9918,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9960,7 +9948,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9971,10 +9959,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9997,13 +9985,13 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -10054,7 +10042,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -10084,7 +10072,7 @@
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -10095,10 +10083,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -10121,16 +10109,16 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -10156,17 +10144,17 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -10176,7 +10164,7 @@
         <v>143</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>93</v>
@@ -10200,30 +10188,30 @@
         <v>84</v>
       </c>
       <c r="AN55" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AO55" t="s" s="2">
+      <c r="AR55" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AR55" t="s" s="2">
-        <v>391</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>84</v>
@@ -10245,16 +10233,16 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -10280,11 +10268,11 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -10302,7 +10290,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>93</v>
@@ -10326,27 +10314,27 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AO56" t="s" s="2">
+      <c r="AR56" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AR56" t="s" s="2">
-        <v>391</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10467,10 +10455,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10593,10 +10581,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10622,16 +10610,16 @@
         <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O59" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10680,7 +10668,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10710,21 +10698,21 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10845,10 +10833,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10971,10 +10959,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -11019,7 +11007,7 @@
         <v>84</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>84</v>
@@ -11073,7 +11061,7 @@
         <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>84</v>
@@ -11099,10 +11087,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11225,10 +11213,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11325,13 +11313,13 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>84</v>
@@ -11340,21 +11328,21 @@
         <v>84</v>
       </c>
       <c r="AP64" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR64" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR64" t="s" s="2">
-        <v>214</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11380,14 +11368,14 @@
         <v>153</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -11436,7 +11424,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -11466,21 +11454,21 @@
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR65" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AQ65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR65" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11503,19 +11491,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -11564,7 +11552,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11594,21 +11582,21 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR66" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR66" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11634,16 +11622,16 @@
         <v>153</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="O67" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -11692,7 +11680,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11707,13 +11695,13 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>84</v>
@@ -11722,21 +11710,21 @@
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11759,16 +11747,16 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11818,7 +11806,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>93</v>
@@ -11833,36 +11821,36 @@
         <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AM68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AP68" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AO68" t="s" s="2">
+      <c r="AQ68" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AP68" t="s" s="2">
+      <c r="AR68" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>447</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11885,16 +11873,16 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11944,7 +11932,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11968,27 +11956,27 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AO69" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AP69" t="s" s="2">
+      <c r="AR69" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AR69" t="s" s="2">
-        <v>456</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -12011,13 +11999,13 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -12068,7 +12056,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -12092,16 +12080,16 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>84</v>
@@ -12109,10 +12097,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12135,13 +12123,13 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -12192,7 +12180,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -12207,36 +12195,36 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AN71" t="s" s="2">
+      <c r="AP71" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AO71" t="s" s="2">
+      <c r="AQ71" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AP71" t="s" s="2">
+      <c r="AR71" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>473</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12259,13 +12247,13 @@
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -12316,7 +12304,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -12331,25 +12319,25 @@
         <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AL72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AQ72" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>84</v>
@@ -12357,10 +12345,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12383,13 +12371,13 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -12440,7 +12428,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -12464,16 +12452,16 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AQ73" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>84</v>
@@ -12481,10 +12469,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12507,16 +12495,16 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12542,13 +12530,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -12566,7 +12554,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12590,13 +12578,13 @@
         <v>84</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12607,10 +12595,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12633,13 +12621,13 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -12690,7 +12678,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12720,10 +12708,10 @@
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>84</v>
@@ -12731,10 +12719,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12757,16 +12745,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12792,13 +12780,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12816,7 +12804,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12840,27 +12828,27 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AO76" t="s" s="2">
+      <c r="AQ76" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AP76" t="s" s="2">
+      <c r="AR76" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>514</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12981,10 +12969,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13107,10 +13095,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13136,16 +13124,16 @@
         <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O79" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -13194,7 +13182,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -13224,21 +13212,21 @@
         <v>84</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13264,16 +13252,16 @@
         <v>153</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="O80" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -13322,7 +13310,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -13337,10 +13325,10 @@
         <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>84</v>
@@ -13352,21 +13340,21 @@
         <v>84</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13389,16 +13377,16 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13448,7 +13436,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13472,16 +13460,16 @@
         <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>84</v>
@@ -13489,10 +13477,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13515,13 +13503,13 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13572,7 +13560,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13596,13 +13584,13 @@
         <v>84</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13613,10 +13601,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13642,10 +13630,10 @@
         <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -13696,7 +13684,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13726,7 +13714,7 @@
         <v>84</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13737,10 +13725,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13763,13 +13751,13 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -13820,7 +13808,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13844,13 +13832,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13861,10 +13849,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13887,17 +13875,17 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13946,7 +13934,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13970,13 +13958,13 @@
         <v>84</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13987,10 +13975,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -14013,16 +14001,16 @@
         <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -14048,13 +14036,13 @@
         <v>84</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>84</v>
@@ -14072,7 +14060,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -14102,7 +14090,7 @@
         <v>84</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -14113,10 +14101,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14139,13 +14127,13 @@
         <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -14196,7 +14184,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -14220,13 +14208,13 @@
         <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -14237,10 +14225,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14263,13 +14251,13 @@
         <v>84</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -14320,7 +14308,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -14344,13 +14332,13 @@
         <v>84</v>
       </c>
       <c r="AN88" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AP88" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -14361,10 +14349,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14387,16 +14375,16 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -14446,7 +14434,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14470,13 +14458,13 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14487,10 +14475,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14611,10 +14599,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14737,14 +14725,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14766,16 +14754,16 @@
         <v>139</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14824,7 +14812,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14865,10 +14853,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14891,17 +14879,17 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14950,7 +14938,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14980,21 +14968,21 @@
         <v>84</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -15020,14 +15008,14 @@
         <v>153</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -15076,7 +15064,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -15091,7 +15079,7 @@
         <v>106</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>84</v>
@@ -15106,21 +15094,21 @@
         <v>84</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15143,19 +15131,19 @@
         <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -15180,31 +15168,31 @@
         <v>84</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -15234,21 +15222,21 @@
         <v>84</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15274,10 +15262,10 @@
         <v>153</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -15328,7 +15316,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -15343,13 +15331,13 @@
         <v>106</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>612</v>
+        <v>84</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>84</v>
@@ -15358,21 +15346,21 @@
         <v>84</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15395,19 +15383,19 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15456,7 +15444,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15486,7 +15474,7 @@
         <v>84</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -15497,10 +15485,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15523,16 +15511,16 @@
         <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="N98" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -15558,13 +15546,13 @@
         <v>84</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -15582,7 +15570,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15612,21 +15600,21 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15649,19 +15637,19 @@
         <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="O99" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
@@ -15686,13 +15674,13 @@
         <v>84</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>84</v>
@@ -15710,7 +15698,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15740,21 +15728,21 @@
         <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15777,17 +15765,17 @@
         <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
@@ -15812,13 +15800,13 @@
         <v>84</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15836,7 +15824,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15866,21 +15854,21 @@
         <v>84</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR100" t="s" s="2">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -16001,10 +15989,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -16127,10 +16115,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16156,16 +16144,16 @@
         <v>171</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O103" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -16214,7 +16202,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -16244,21 +16232,21 @@
         <v>84</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16379,10 +16367,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16505,10 +16493,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16553,7 +16541,7 @@
         <v>84</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>84</v>
@@ -16607,7 +16595,7 @@
         <v>106</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>84</v>
@@ -16633,10 +16621,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16759,10 +16747,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16859,13 +16847,13 @@
         <v>106</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>84</v>
@@ -16874,21 +16862,21 @@
         <v>84</v>
       </c>
       <c r="AP108" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AQ108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR108" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AQ108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR108" t="s" s="2">
-        <v>214</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16914,14 +16902,14 @@
         <v>153</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
@@ -16970,7 +16958,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -17000,21 +16988,21 @@
         <v>84</v>
       </c>
       <c r="AP109" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AQ109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR109" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AQ109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR109" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17037,19 +17025,19 @@
         <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -17098,7 +17086,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -17128,21 +17116,21 @@
         <v>84</v>
       </c>
       <c r="AP110" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AQ110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR110" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AQ110" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR110" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17168,16 +17156,16 @@
         <v>153</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="O111" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -17226,7 +17214,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -17256,21 +17244,21 @@
         <v>84</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR111" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17293,19 +17281,19 @@
         <v>94</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="O112" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>84</v>
@@ -17330,13 +17318,13 @@
         <v>84</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>84</v>
@@ -17354,7 +17342,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -17384,21 +17372,21 @@
         <v>84</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR112" t="s" s="2">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17421,13 +17409,13 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -17478,7 +17466,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17514,15 +17502,15 @@
         <v>84</v>
       </c>
       <c r="AR113" t="s" s="2">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17643,10 +17631,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17769,13 +17757,13 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>84</v>
@@ -17797,16 +17785,16 @@
         <v>84</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N116" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -17897,10 +17885,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -18021,10 +18009,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18145,10 +18133,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18188,7 +18176,7 @@
       </c>
       <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="S119" t="s" s="2">
         <v>84</v>
@@ -18271,10 +18259,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18297,13 +18285,13 @@
         <v>84</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>172</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -18363,19 +18351,19 @@
         <v>93</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>84</v>
@@ -18395,10 +18383,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18421,17 +18409,17 @@
         <v>94</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>84</v>
@@ -18456,13 +18444,13 @@
         <v>84</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>84</v>
@@ -18480,7 +18468,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18516,15 +18504,15 @@
         <v>84</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18547,19 +18535,19 @@
         <v>94</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="N122" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="O122" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
@@ -18596,7 +18584,7 @@
         <v>84</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
@@ -18606,7 +18594,7 @@
         <v>143</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18636,24 +18624,24 @@
         <v>84</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR122" t="s" s="2">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>84</v>
@@ -18675,19 +18663,19 @@
         <v>84</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="N123" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="L123" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>723</v>
-      </c>
       <c r="O123" t="s" s="2">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>84</v>
@@ -18736,7 +18724,7 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>82</v>
@@ -18748,7 +18736,7 @@
         <v>150</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>84</v>
@@ -18766,21 +18754,21 @@
         <v>84</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR123" t="s" s="2">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18901,10 +18889,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19027,10 +19015,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19053,19 +19041,19 @@
         <v>94</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="N126" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>734</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -19114,7 +19102,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -19129,13 +19117,13 @@
         <v>106</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>84</v>
@@ -19144,21 +19132,21 @@
         <v>84</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19184,65 +19172,65 @@
         <v>114</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="P127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q127" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="R127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="Z127" t="s" s="2">
         <v>746</v>
       </c>
-      <c r="P127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q127" t="s" s="2">
+      <c r="AA127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF127" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="R127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -19272,21 +19260,21 @@
         <v>84</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR127" t="s" s="2">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19312,14 +19300,14 @@
         <v>153</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
@@ -19368,7 +19356,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -19383,36 +19371,36 @@
         <v>106</v>
       </c>
       <c r="AK128" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP128" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="AQ128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR128" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP128" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="AQ128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR128" t="s" s="2">
-        <v>762</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19438,14 +19426,14 @@
         <v>108</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19494,7 +19482,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19503,7 +19491,7 @@
         <v>93</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>106</v>
@@ -19524,21 +19512,21 @@
         <v>84</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR129" t="s" s="2">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19564,16 +19552,16 @@
         <v>114</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="O130" t="s" s="2">
         <v>773</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>776</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
@@ -19622,7 +19610,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19652,21 +19640,21 @@
         <v>84</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR130" t="s" s="2">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19689,19 +19677,19 @@
         <v>94</v>
       </c>
       <c r="K131" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>780</v>
       </c>
-      <c r="L131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>84</v>
@@ -19750,7 +19738,7 @@
         <v>84</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>82</v>
@@ -19780,21 +19768,21 @@
         <v>84</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="AQ131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR131" t="s" s="2">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19817,19 +19805,19 @@
         <v>94</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="N132" t="s" s="2">
         <v>789</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="O132" t="s" s="2">
         <v>790</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>793</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
@@ -19878,7 +19866,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -19908,21 +19896,21 @@
         <v>84</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR132" t="s" s="2">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19945,19 +19933,19 @@
         <v>94</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="O133" t="s" s="2">
         <v>798</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>801</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
@@ -20006,7 +19994,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -20036,7 +20024,7 @@
         <v>84</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>84</v>
@@ -20047,10 +20035,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20073,17 +20061,17 @@
         <v>94</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -20132,7 +20120,7 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
@@ -20162,7 +20150,7 @@
         <v>84</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>84</v>
@@ -20173,10 +20161,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20199,13 +20187,13 @@
         <v>84</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -20256,7 +20244,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -20283,10 +20271,10 @@
         <v>84</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>84</v>
@@ -20297,10 +20285,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20421,10 +20409,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20547,14 +20535,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -20576,16 +20564,16 @@
         <v>139</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>84</v>
@@ -20634,7 +20622,7 @@
         <v>84</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>82</v>
@@ -20675,10 +20663,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20701,16 +20689,16 @@
         <v>84</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -20760,7 +20748,7 @@
         <v>84</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>82</v>
@@ -20790,7 +20778,7 @@
         <v>84</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="AQ139" t="s" s="2">
         <v>84</v>
@@ -20801,10 +20789,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20925,10 +20913,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21051,14 +21039,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -21080,16 +21068,16 @@
         <v>139</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>84</v>
@@ -21138,7 +21126,7 @@
         <v>84</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>82</v>
@@ -21179,10 +21167,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21205,13 +21193,13 @@
         <v>84</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -21262,7 +21250,7 @@
         <v>84</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>82</v>
@@ -21292,7 +21280,7 @@
         <v>84</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="AQ143" t="s" s="2">
         <v>84</v>
@@ -21303,10 +21291,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21329,13 +21317,13 @@
         <v>84</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -21386,7 +21374,7 @@
         <v>84</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>82</v>
@@ -21416,7 +21404,7 @@
         <v>84</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="AQ144" t="s" s="2">
         <v>84</v>
@@ -21427,10 +21415,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21453,13 +21441,13 @@
         <v>84</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -21510,7 +21498,7 @@
         <v>84</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>82</v>
@@ -21540,7 +21528,7 @@
         <v>84</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="AQ145" t="s" s="2">
         <v>84</v>
@@ -21551,10 +21539,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21577,19 +21565,19 @@
         <v>84</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="N146" t="s" s="2">
         <v>839</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="O146" t="s" s="2">
         <v>840</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>843</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>84</v>
@@ -21638,7 +21626,7 @@
         <v>84</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>82</v>
@@ -21665,10 +21653,10 @@
         <v>84</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="AQ146" t="s" s="2">
         <v>84</v>
@@ -21679,10 +21667,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21803,10 +21791,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21929,10 +21917,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21955,16 +21943,16 @@
         <v>94</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -22014,7 +22002,7 @@
         <v>84</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>82</v>
@@ -22023,7 +22011,7 @@
         <v>93</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>106</v>
@@ -22044,21 +22032,21 @@
         <v>84</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="AQ149" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR149" t="s" s="2">
-        <v>855</v>
+        <v>852</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22081,23 +22069,23 @@
         <v>94</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q150" t="s" s="2">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="R150" t="s" s="2">
         <v>84</v>
@@ -22142,7 +22130,7 @@
         <v>84</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>82</v>
@@ -22151,42 +22139,42 @@
         <v>93</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK150" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>860</v>
+      </c>
+      <c r="AN150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP150" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="AQ150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR150" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="AL150" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="AN150" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO150" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP150" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="AQ150" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR150" t="s" s="2">
-        <v>865</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22209,16 +22197,16 @@
         <v>84</v>
       </c>
       <c r="K151" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="N151" t="s" s="2">
         <v>867</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>870</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -22268,7 +22256,7 @@
         <v>84</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>82</v>
@@ -22283,36 +22271,36 @@
         <v>106</v>
       </c>
       <c r="AK151" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>869</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO151" t="s" s="2">
+        <v>870</v>
+      </c>
+      <c r="AP151" t="s" s="2">
         <v>871</v>
       </c>
-      <c r="AL151" t="s" s="2">
+      <c r="AQ151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR151" t="s" s="2">
         <v>872</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO151" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="AP151" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="AQ151" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR151" t="s" s="2">
-        <v>876</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22335,13 +22323,13 @@
         <v>84</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -22392,7 +22380,7 @@
         <v>84</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>82</v>
@@ -22419,24 +22407,24 @@
         <v>84</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR152" t="s" s="2">
-        <v>882</v>
+        <v>878</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22557,10 +22545,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22683,10 +22671,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22709,19 +22697,19 @@
         <v>94</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="N155" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="L155" t="s" s="2">
+      <c r="O155" t="s" s="2">
         <v>734</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>84</v>
@@ -22770,7 +22758,7 @@
         <v>84</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>82</v>
@@ -22785,13 +22773,13 @@
         <v>106</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>84</v>
@@ -22800,21 +22788,21 @@
         <v>84</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="AQ155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR155" t="s" s="2">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22840,65 +22828,65 @@
         <v>114</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="P156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q156" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="R156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="Z156" t="s" s="2">
         <v>746</v>
       </c>
-      <c r="P156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q156" t="s" s="2">
+      <c r="AA156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF156" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="R156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>82</v>
@@ -22928,21 +22916,21 @@
         <v>84</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="AQ156" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR156" t="s" s="2">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22968,14 +22956,14 @@
         <v>153</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>84</v>
@@ -23024,7 +23012,7 @@
         <v>84</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>82</v>
@@ -23054,21 +23042,21 @@
         <v>84</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="AQ157" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR157" t="s" s="2">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23094,14 +23082,14 @@
         <v>108</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>84</v>
@@ -23150,7 +23138,7 @@
         <v>84</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>82</v>
@@ -23159,7 +23147,7 @@
         <v>93</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>106</v>
@@ -23180,21 +23168,21 @@
         <v>84</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="AQ158" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR158" t="s" s="2">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23220,16 +23208,16 @@
         <v>114</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="O159" t="s" s="2">
         <v>773</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>776</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>84</v>
@@ -23278,7 +23266,7 @@
         <v>84</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>82</v>
@@ -23308,21 +23296,21 @@
         <v>84</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="AQ159" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR159" t="s" s="2">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23345,16 +23333,16 @@
         <v>84</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -23404,7 +23392,7 @@
         <v>84</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
@@ -23419,22 +23407,22 @@
         <v>106</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="AQ160" t="s" s="2">
         <v>84</v>
@@ -23445,10 +23433,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23471,13 +23459,13 @@
         <v>84</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -23528,7 +23516,7 @@
         <v>84</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>82</v>
@@ -23558,10 +23546,10 @@
         <v>84</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AR161" t="s" s="2">
         <v>84</v>
@@ -23569,10 +23557,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23595,13 +23583,13 @@
         <v>84</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23652,7 +23640,7 @@
         <v>84</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23679,10 +23667,10 @@
         <v>84</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>84</v>
@@ -23693,10 +23681,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23817,10 +23805,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23943,14 +23931,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -23972,16 +23960,16 @@
         <v>139</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="N165" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>84</v>
@@ -24030,7 +24018,7 @@
         <v>84</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>82</v>
@@ -24071,10 +24059,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24097,16 +24085,16 @@
         <v>84</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -24132,13 +24120,13 @@
         <v>84</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>84</v>
@@ -24156,7 +24144,7 @@
         <v>84</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>93</v>
@@ -24183,24 +24171,24 @@
         <v>84</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="AQ166" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR166" t="s" s="2">
-        <v>920</v>
+        <v>916</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24223,13 +24211,13 @@
         <v>84</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -24256,13 +24244,13 @@
         <v>84</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>84</v>
@@ -24280,7 +24268,7 @@
         <v>84</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>82</v>
@@ -24307,24 +24295,24 @@
         <v>84</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="AQ167" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR167" t="s" s="2">
-        <v>928</v>
+        <v>924</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24347,13 +24335,13 @@
         <v>84</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -24404,7 +24392,7 @@
         <v>84</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -24428,13 +24416,13 @@
         <v>84</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="AQ168" t="s" s="2">
         <v>84</v>
@@ -24445,14 +24433,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -24471,16 +24459,16 @@
         <v>84</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -24530,7 +24518,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>82</v>
@@ -24560,7 +24548,7 @@
         <v>84</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>84</v>
@@ -24571,10 +24559,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24597,16 +24585,16 @@
         <v>84</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -24656,7 +24644,7 @@
         <v>84</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>82</v>
@@ -24680,13 +24668,13 @@
         <v>84</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="AQ170" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="949">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,6 +676,9 @@
     <t>RxOut.RxOutpat.RxStatus</t>
   </si>
   <si>
+    <t>Medication.PharmacyStatus,Medication.VAStatus</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
@@ -775,6 +778,9 @@
     <t>RxOut.RxOutpat.CancelDate</t>
   </si>
   <si>
+    <t>Medication.ToTime,Medication.DiscontinuedDateTime</t>
+  </si>
+  <si>
     <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig</t>
   </si>
   <si>
@@ -969,7 +975,7 @@
     <t>RxOut.RxOutpat.RxNumber</t>
   </si>
   <si>
-    <t>pharmacy (med).dose,med.dose</t>
+    <t>Medication.PrescriptionNumber,Medication.FillDate</t>
   </si>
   <si>
     <t>Request.identifier</t>
@@ -1329,7 +1335,7 @@
     <t>RxOut.RxOutpat.LocalDrugIEN,RxOut.RxOutpat.NationalDrugIEN,RxOut.RxOutpatFill.LocalDrugIEN,RxOut.RxOutpatFill.NationalDrugIEN</t>
   </si>
   <si>
-    <t>pharmacy (med).route,med.route</t>
+    <t>Medication.DrugProduct,Medication.CMOP</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.display</t>
@@ -1394,9 +1400,6 @@
   </si>
   <si>
     <t>RxOut.ActivityLog.PatientIEN,RxOut.ActivityLogOtherComments.PatientIEN,RxOut.RxOutpat.PatientIEN,RxOut.RxOutpatExt.PatientIEN,RxOut.RxOutpatExt.PatientSID,RxOut.RxOutpatFill.PatientIEN,RxOut.RxOutpatMedInstructions.PatientIEN,RxOut.RxOutpatSig.PatientIEN</t>
-  </si>
-  <si>
-    <t>pharmacy (med).units,med.units</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -1478,7 +1481,7 @@
     <t>RxOut.ActivityLog.IssueDateTime,RxOut.RxOutpat.IssueDate,RxOut.RxOutpatExt.IssueDateTime,RxOut.RxOutpatFill.IssueDate,RxOut.RxOutpatMedInstructions.IssueDate,RxOut.RxOutpatSig.IssueDate</t>
   </si>
   <si>
-    <t>pharmacy (med).unitsPerDose,med.unitsPerDose</t>
+    <t>Medication.VAStartDate,Medication.FillQuantity</t>
   </si>
   <si>
     <t>Request.authoredOn</t>
@@ -1515,7 +1518,7 @@
     <t>RxOut.RxOutpat.ProviderIEN</t>
   </si>
   <si>
-    <t>pharmacy (med).currentProvider,pharmacy (med).doseStart,pharmacy (med).doseStop,pharmacy (med).duration,med.currentProvider,med.doseStart,med.doseStop,med.duration</t>
+    <t>Medication.OrderedBy</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -1640,6 +1643,9 @@
     <t>RxOut.RxOutpatExt.IndicationForUse</t>
   </si>
   <si>
+    <t>Medication.Indication</t>
+  </si>
+  <si>
     <t>MedicationRequest.reasonReference</t>
   </si>
   <si>
@@ -1921,6 +1927,9 @@
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
   </si>
   <si>
+    <t>Medication.TextInstruction</t>
+  </si>
+  <si>
     <t>MedicationRequest.dosageInstruction.timing</t>
   </si>
   <si>
@@ -2070,7 +2079,7 @@
     <t>RxOut.RxOutpatMedInstructions.MedRoute</t>
   </si>
   <si>
-    <t>pharmacy (med).dose [m],med.dose [m]</t>
+    <t>Medication.DosageSteps,Medication.Route,Medication.DoseQuantity,Medication.DoseUoM,Medication.Duration,Medication.Frequency,Medication.TextInstruction,Medication.Conjunction,Medication.Noun,Medication.UnitsPerDose,Medication.Verb</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.route.coding.display</t>
@@ -2690,7 +2699,7 @@
     <t>815: source value from PRESCRIPTION - EXPIRATION DATE (52-26)</t>
   </si>
   <si>
-    <t>pharmacy (med).expires,med.expires</t>
+    <t>Medication.ToTime,Medication.Expires</t>
   </si>
   <si>
     <t>./high</t>
@@ -2721,6 +2730,9 @@
     <t>RxOut.RxOutpat.MaxRefills</t>
   </si>
   <si>
+    <t>Medication.NumberOfRefills</t>
+  </si>
+  <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Quantity</t>
   </si>
   <si>
@@ -2760,7 +2772,7 @@
     <t>1669: source value from PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
-    <t>pharmacy (med).schedule,med.schedule</t>
+    <t>Medication.OrderQuantity</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.quantity.comparator</t>
@@ -2790,7 +2802,7 @@
     <t>1670: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
   </si>
   <si>
-    <t>pharmacy (med).daysSupply,med.daysSupply</t>
+    <t>Medication.DaysSupply</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Substitutions</t>
@@ -3305,7 +3317,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="175.39453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="166.08984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="226.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -5685,7 +5697,7 @@
         <v>211</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>84</v>
@@ -5694,21 +5706,21 @@
         <v>84</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5734,14 +5746,14 @@
         <v>153</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -5790,7 +5802,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5820,21 +5832,21 @@
         <v>84</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5857,19 +5869,19 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -5918,7 +5930,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5948,24 +5960,24 @@
         <v>84</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>84</v>
@@ -5987,13 +5999,13 @@
         <v>84</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -6085,7 +6097,7 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>152</v>
@@ -6209,7 +6221,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>159</v>
@@ -6333,7 +6345,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>163</v>
@@ -6376,7 +6388,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>84</v>
@@ -6459,7 +6471,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>170</v>
@@ -6485,7 +6497,7 @@
         <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>172</v>
@@ -6557,13 +6569,13 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>84</v>
@@ -6583,13 +6595,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>84</v>
@@ -6611,13 +6623,13 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6709,7 +6721,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>152</v>
@@ -6833,7 +6845,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>159</v>
@@ -6957,7 +6969,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>163</v>
@@ -7000,7 +7012,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>84</v>
@@ -7083,7 +7095,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>170</v>
@@ -7109,7 +7121,7 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>172</v>
@@ -7181,10 +7193,10 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>84</v>
@@ -7207,7 +7219,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>176</v>
@@ -7236,10 +7248,10 @@
         <v>153</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -7331,7 +7343,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>178</v>
@@ -7453,13 +7465,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -7481,16 +7493,16 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -7581,10 +7593,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7705,10 +7717,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7829,10 +7841,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7872,7 +7884,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>84</v>
@@ -7955,10 +7967,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7981,13 +7993,13 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>172</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7999,7 +8011,7 @@
         <v>84</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>84</v>
@@ -8047,7 +8059,7 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -8079,10 +8091,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -8105,13 +8117,13 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -8162,7 +8174,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -8203,13 +8215,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>84</v>
@@ -8231,13 +8243,13 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -8329,7 +8341,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>152</v>
@@ -8453,7 +8465,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>159</v>
@@ -8577,7 +8589,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>163</v>
@@ -8620,7 +8632,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>84</v>
@@ -8703,7 +8715,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>170</v>
@@ -8729,7 +8741,7 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>172</v>
@@ -8801,7 +8813,7 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>84</v>
@@ -8827,10 +8839,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8856,16 +8868,16 @@
         <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8914,7 +8926,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8955,10 +8967,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8981,16 +8993,16 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -9040,7 +9052,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -9055,36 +9067,36 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -9110,13 +9122,13 @@
         <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -9142,11 +9154,11 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -9164,7 +9176,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>93</v>
@@ -9179,25 +9191,25 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>211</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -9205,10 +9217,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9231,16 +9243,16 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -9266,13 +9278,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -9290,7 +9302,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -9314,13 +9326,13 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -9331,10 +9343,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9360,13 +9372,13 @@
         <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -9377,7 +9389,7 @@
         <v>84</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>84</v>
@@ -9392,13 +9404,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -9416,7 +9428,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>93</v>
@@ -9431,7 +9443,7 @@
         <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>84</v>
@@ -9440,16 +9452,16 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -9457,10 +9469,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9483,16 +9495,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -9503,7 +9515,7 @@
         <v>84</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>84</v>
@@ -9518,19 +9530,19 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -9540,7 +9552,7 @@
         <v>143</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9555,7 +9567,7 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>84</v>
@@ -9567,13 +9579,13 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -9581,13 +9593,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>84</v>
@@ -9609,16 +9621,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9644,13 +9656,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -9668,7 +9680,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9695,13 +9707,13 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9709,10 +9721,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9738,10 +9750,10 @@
         <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9768,13 +9780,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -9792,7 +9804,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9816,16 +9828,16 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9833,10 +9845,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9859,16 +9871,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9918,7 +9930,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9948,7 +9960,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9959,10 +9971,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9985,13 +9997,13 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -10042,7 +10054,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -10072,7 +10084,7 @@
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -10083,10 +10095,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -10109,16 +10121,16 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -10144,17 +10156,17 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -10164,7 +10176,7 @@
         <v>143</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>93</v>
@@ -10188,30 +10200,30 @@
         <v>84</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>84</v>
@@ -10233,16 +10245,16 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -10268,11 +10280,11 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -10290,7 +10302,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>93</v>
@@ -10314,27 +10326,27 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10455,10 +10467,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10581,10 +10593,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10610,16 +10622,16 @@
         <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10668,7 +10680,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10698,21 +10710,21 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10833,10 +10845,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10959,10 +10971,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -11007,7 +11019,7 @@
         <v>84</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>84</v>
@@ -11061,7 +11073,7 @@
         <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>84</v>
@@ -11087,10 +11099,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11213,10 +11225,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11313,13 +11325,13 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>84</v>
@@ -11328,21 +11340,21 @@
         <v>84</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11368,14 +11380,14 @@
         <v>153</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -11424,7 +11436,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -11454,21 +11466,21 @@
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11491,19 +11503,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -11552,7 +11564,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11582,21 +11594,21 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11622,16 +11634,16 @@
         <v>153</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -11680,7 +11692,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11695,13 +11707,13 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>84</v>
@@ -11710,21 +11722,21 @@
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11747,16 +11759,16 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11806,7 +11818,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>93</v>
@@ -11821,36 +11833,36 @@
         <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>440</v>
+        <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11873,16 +11885,16 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11932,7 +11944,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11956,27 +11968,27 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11999,13 +12011,13 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -12056,7 +12068,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -12080,16 +12092,16 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>84</v>
@@ -12097,10 +12109,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12123,13 +12135,13 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -12180,7 +12192,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -12195,36 +12207,36 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12247,13 +12259,13 @@
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -12304,7 +12316,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -12319,25 +12331,25 @@
         <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>84</v>
@@ -12345,10 +12357,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12371,13 +12383,13 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -12428,7 +12440,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -12452,16 +12464,16 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>84</v>
@@ -12469,10 +12481,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12495,16 +12507,16 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12530,13 +12542,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -12554,7 +12566,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12578,13 +12590,13 @@
         <v>84</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12595,10 +12607,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12621,13 +12633,13 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -12678,7 +12690,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12708,10 +12720,10 @@
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>84</v>
@@ -12719,10 +12731,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12745,16 +12757,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12780,13 +12792,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12804,7 +12816,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12828,27 +12840,27 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12969,10 +12981,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13095,10 +13107,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13124,16 +13136,16 @@
         <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -13182,7 +13194,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -13212,21 +13224,21 @@
         <v>84</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13252,16 +13264,16 @@
         <v>153</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -13310,7 +13322,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -13325,13 +13337,13 @@
         <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>84</v>
+        <v>520</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>84</v>
@@ -13340,21 +13352,21 @@
         <v>84</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13377,16 +13389,16 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13436,7 +13448,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13460,16 +13472,16 @@
         <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>84</v>
@@ -13477,10 +13489,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13503,13 +13515,13 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13560,7 +13572,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13584,13 +13596,13 @@
         <v>84</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13601,10 +13613,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13630,10 +13642,10 @@
         <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -13684,7 +13696,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13714,7 +13726,7 @@
         <v>84</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13725,10 +13737,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13751,13 +13763,13 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -13808,7 +13820,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13832,13 +13844,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13849,10 +13861,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13875,17 +13887,17 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13934,7 +13946,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13958,13 +13970,13 @@
         <v>84</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13975,10 +13987,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -14001,16 +14013,16 @@
         <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -14036,13 +14048,13 @@
         <v>84</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>84</v>
@@ -14060,7 +14072,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -14090,7 +14102,7 @@
         <v>84</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -14101,10 +14113,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14127,13 +14139,13 @@
         <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -14184,7 +14196,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -14208,13 +14220,13 @@
         <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -14225,10 +14237,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14251,13 +14263,13 @@
         <v>84</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -14308,7 +14320,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -14332,13 +14344,13 @@
         <v>84</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -14349,10 +14361,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14375,16 +14387,16 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -14434,7 +14446,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14458,13 +14470,13 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14475,10 +14487,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14599,10 +14611,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14725,14 +14737,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14754,16 +14766,16 @@
         <v>139</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14812,7 +14824,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14853,10 +14865,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14879,17 +14891,17 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14938,7 +14950,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14968,21 +14980,21 @@
         <v>84</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -15008,14 +15020,14 @@
         <v>153</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -15064,7 +15076,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -15079,7 +15091,7 @@
         <v>106</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>84</v>
@@ -15094,21 +15106,21 @@
         <v>84</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15131,19 +15143,19 @@
         <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -15168,13 +15180,13 @@
         <v>84</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -15192,7 +15204,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -15222,21 +15234,21 @@
         <v>84</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15262,10 +15274,10 @@
         <v>153</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -15316,7 +15328,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -15331,13 +15343,13 @@
         <v>106</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>84</v>
+        <v>612</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>84</v>
@@ -15346,21 +15358,21 @@
         <v>84</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15383,19 +15395,19 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15444,7 +15456,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15474,7 +15486,7 @@
         <v>84</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -15485,10 +15497,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15511,16 +15523,16 @@
         <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -15546,13 +15558,13 @@
         <v>84</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -15570,7 +15582,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15600,21 +15612,21 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15637,19 +15649,19 @@
         <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
@@ -15674,13 +15686,13 @@
         <v>84</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>84</v>
@@ -15698,7 +15710,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15728,21 +15740,21 @@
         <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15765,17 +15777,17 @@
         <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
@@ -15800,13 +15812,13 @@
         <v>84</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15824,7 +15836,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15854,21 +15866,21 @@
         <v>84</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR100" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15989,10 +16001,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -16115,10 +16127,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16144,16 +16156,16 @@
         <v>171</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -16202,7 +16214,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -16232,21 +16244,21 @@
         <v>84</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16367,10 +16379,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16493,10 +16505,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16541,7 +16553,7 @@
         <v>84</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>84</v>
@@ -16595,7 +16607,7 @@
         <v>106</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>84</v>
@@ -16621,10 +16633,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16747,10 +16759,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16847,13 +16859,13 @@
         <v>106</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>84</v>
@@ -16862,21 +16874,21 @@
         <v>84</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16902,14 +16914,14 @@
         <v>153</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
@@ -16958,7 +16970,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16988,21 +17000,21 @@
         <v>84</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17025,19 +17037,19 @@
         <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -17086,7 +17098,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -17116,21 +17128,21 @@
         <v>84</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17156,16 +17168,16 @@
         <v>153</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -17214,7 +17226,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -17244,21 +17256,21 @@
         <v>84</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR111" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17281,19 +17293,19 @@
         <v>94</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>84</v>
@@ -17318,13 +17330,13 @@
         <v>84</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>84</v>
@@ -17342,7 +17354,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -17372,21 +17384,21 @@
         <v>84</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR112" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17409,13 +17421,13 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -17466,7 +17478,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17502,15 +17514,15 @@
         <v>84</v>
       </c>
       <c r="AR113" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17631,10 +17643,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17757,13 +17769,13 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>84</v>
@@ -17785,16 +17797,16 @@
         <v>84</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -17885,10 +17897,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -18009,10 +18021,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18133,10 +18145,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18176,7 +18188,7 @@
       </c>
       <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="S119" t="s" s="2">
         <v>84</v>
@@ -18259,10 +18271,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18285,13 +18297,13 @@
         <v>84</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>172</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -18351,19 +18363,19 @@
         <v>93</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>84</v>
@@ -18383,10 +18395,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18409,17 +18421,17 @@
         <v>94</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>84</v>
@@ -18444,13 +18456,13 @@
         <v>84</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>84</v>
@@ -18468,7 +18480,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18504,15 +18516,15 @@
         <v>84</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18535,19 +18547,19 @@
         <v>94</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
@@ -18584,7 +18596,7 @@
         <v>84</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
@@ -18594,7 +18606,7 @@
         <v>143</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18624,24 +18636,24 @@
         <v>84</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR122" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>84</v>
@@ -18663,19 +18675,19 @@
         <v>84</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>84</v>
@@ -18724,7 +18736,7 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>82</v>
@@ -18736,7 +18748,7 @@
         <v>150</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>84</v>
@@ -18754,21 +18766,21 @@
         <v>84</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR123" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18889,10 +18901,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19015,10 +19027,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19041,19 +19053,19 @@
         <v>94</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -19102,7 +19114,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -19117,13 +19129,13 @@
         <v>106</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>84</v>
@@ -19132,21 +19144,21 @@
         <v>84</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19172,20 +19184,20 @@
         <v>114</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q127" t="s" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="R127" t="s" s="2">
         <v>84</v>
@@ -19206,13 +19218,13 @@
         <v>84</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>84</v>
@@ -19230,7 +19242,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -19260,21 +19272,21 @@
         <v>84</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR127" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19300,14 +19312,14 @@
         <v>153</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
@@ -19356,7 +19368,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -19371,13 +19383,13 @@
         <v>106</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>84</v>
@@ -19386,21 +19398,21 @@
         <v>84</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR128" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19426,14 +19438,14 @@
         <v>108</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19482,7 +19494,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19491,7 +19503,7 @@
         <v>93</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>106</v>
@@ -19512,21 +19524,21 @@
         <v>84</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR129" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19552,16 +19564,16 @@
         <v>114</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
@@ -19610,7 +19622,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19640,21 +19652,21 @@
         <v>84</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR130" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19677,19 +19689,19 @@
         <v>94</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>84</v>
@@ -19738,7 +19750,7 @@
         <v>84</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>82</v>
@@ -19768,21 +19780,21 @@
         <v>84</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="AQ131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR131" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19805,19 +19817,19 @@
         <v>94</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
@@ -19866,7 +19878,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -19896,21 +19908,21 @@
         <v>84</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR132" t="s" s="2">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19933,19 +19945,19 @@
         <v>94</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
@@ -19994,7 +20006,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -20024,7 +20036,7 @@
         <v>84</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>84</v>
@@ -20035,10 +20047,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20061,17 +20073,17 @@
         <v>94</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -20120,7 +20132,7 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
@@ -20150,7 +20162,7 @@
         <v>84</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>84</v>
@@ -20161,10 +20173,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20187,13 +20199,13 @@
         <v>84</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -20244,7 +20256,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -20271,10 +20283,10 @@
         <v>84</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>84</v>
@@ -20285,10 +20297,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20409,10 +20421,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20535,14 +20547,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -20564,16 +20576,16 @@
         <v>139</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>84</v>
@@ -20622,7 +20634,7 @@
         <v>84</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>82</v>
@@ -20663,10 +20675,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20689,16 +20701,16 @@
         <v>84</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -20748,7 +20760,7 @@
         <v>84</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>82</v>
@@ -20778,7 +20790,7 @@
         <v>84</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="AQ139" t="s" s="2">
         <v>84</v>
@@ -20789,10 +20801,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20913,10 +20925,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21039,14 +21051,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -21068,16 +21080,16 @@
         <v>139</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>84</v>
@@ -21126,7 +21138,7 @@
         <v>84</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>82</v>
@@ -21167,10 +21179,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21193,13 +21205,13 @@
         <v>84</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -21250,7 +21262,7 @@
         <v>84</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>82</v>
@@ -21280,7 +21292,7 @@
         <v>84</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="AQ143" t="s" s="2">
         <v>84</v>
@@ -21291,10 +21303,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21317,13 +21329,13 @@
         <v>84</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -21374,7 +21386,7 @@
         <v>84</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>82</v>
@@ -21404,7 +21416,7 @@
         <v>84</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="AQ144" t="s" s="2">
         <v>84</v>
@@ -21415,10 +21427,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21441,13 +21453,13 @@
         <v>84</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -21498,7 +21510,7 @@
         <v>84</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>82</v>
@@ -21528,7 +21540,7 @@
         <v>84</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="AQ145" t="s" s="2">
         <v>84</v>
@@ -21539,10 +21551,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21565,19 +21577,19 @@
         <v>84</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>84</v>
@@ -21626,7 +21638,7 @@
         <v>84</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>82</v>
@@ -21653,10 +21665,10 @@
         <v>84</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="AQ146" t="s" s="2">
         <v>84</v>
@@ -21667,10 +21679,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21791,10 +21803,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21917,10 +21929,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21943,16 +21955,16 @@
         <v>94</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -22002,7 +22014,7 @@
         <v>84</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>82</v>
@@ -22011,7 +22023,7 @@
         <v>93</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>106</v>
@@ -22032,21 +22044,21 @@
         <v>84</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="AQ149" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR149" t="s" s="2">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22069,23 +22081,23 @@
         <v>94</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q150" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="R150" t="s" s="2">
         <v>84</v>
@@ -22130,7 +22142,7 @@
         <v>84</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>82</v>
@@ -22139,19 +22151,19 @@
         <v>93</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>84</v>
@@ -22160,21 +22172,21 @@
         <v>84</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="AQ150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR150" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22197,16 +22209,16 @@
         <v>84</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -22256,7 +22268,7 @@
         <v>84</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>82</v>
@@ -22271,36 +22283,36 @@
         <v>106</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>84</v>
+        <v>873</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="AQ151" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR151" t="s" s="2">
-        <v>872</v>
+        <v>876</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22323,13 +22335,13 @@
         <v>84</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -22380,7 +22392,7 @@
         <v>84</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>82</v>
@@ -22407,24 +22419,24 @@
         <v>84</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR152" t="s" s="2">
-        <v>878</v>
+        <v>882</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22545,10 +22557,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22671,10 +22683,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22697,19 +22709,19 @@
         <v>94</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>84</v>
@@ -22758,7 +22770,7 @@
         <v>84</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>82</v>
@@ -22773,13 +22785,13 @@
         <v>106</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>84</v>
@@ -22788,21 +22800,21 @@
         <v>84</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="AQ155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR155" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22828,20 +22840,20 @@
         <v>114</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q156" t="s" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="R156" t="s" s="2">
         <v>84</v>
@@ -22862,13 +22874,13 @@
         <v>84</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>84</v>
@@ -22886,7 +22898,7 @@
         <v>84</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>82</v>
@@ -22916,21 +22928,21 @@
         <v>84</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="AQ156" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR156" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22956,14 +22968,14 @@
         <v>153</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>84</v>
@@ -23012,7 +23024,7 @@
         <v>84</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>82</v>
@@ -23042,21 +23054,21 @@
         <v>84</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="AQ157" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR157" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23082,14 +23094,14 @@
         <v>108</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>84</v>
@@ -23138,7 +23150,7 @@
         <v>84</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>82</v>
@@ -23147,7 +23159,7 @@
         <v>93</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>106</v>
@@ -23168,21 +23180,21 @@
         <v>84</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="AQ158" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR158" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23208,16 +23220,16 @@
         <v>114</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>84</v>
@@ -23266,7 +23278,7 @@
         <v>84</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>82</v>
@@ -23296,21 +23308,21 @@
         <v>84</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="AQ159" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR159" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23333,16 +23345,16 @@
         <v>84</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -23392,7 +23404,7 @@
         <v>84</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
@@ -23407,22 +23419,22 @@
         <v>106</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="AQ160" t="s" s="2">
         <v>84</v>
@@ -23433,10 +23445,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23459,13 +23471,13 @@
         <v>84</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -23516,7 +23528,7 @@
         <v>84</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>82</v>
@@ -23546,10 +23558,10 @@
         <v>84</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AR161" t="s" s="2">
         <v>84</v>
@@ -23557,10 +23569,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23583,13 +23595,13 @@
         <v>84</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23640,7 +23652,7 @@
         <v>84</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23667,10 +23679,10 @@
         <v>84</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>84</v>
@@ -23681,10 +23693,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23805,10 +23817,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23931,14 +23943,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -23960,16 +23972,16 @@
         <v>139</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N165" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>84</v>
@@ -24018,7 +24030,7 @@
         <v>84</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>82</v>
@@ -24059,10 +24071,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24085,16 +24097,16 @@
         <v>84</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -24120,31 +24132,31 @@
         <v>84</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y166" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="Z166" t="s" s="2">
+        <v>918</v>
+      </c>
+      <c r="AA166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF166" t="s" s="2">
         <v>913</v>
-      </c>
-      <c r="Z166" t="s" s="2">
-        <v>914</v>
-      </c>
-      <c r="AA166" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB166" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC166" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD166" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE166" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF166" t="s" s="2">
-        <v>909</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>93</v>
@@ -24171,24 +24183,24 @@
         <v>84</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="AQ166" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR166" t="s" s="2">
-        <v>916</v>
+        <v>920</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24211,13 +24223,13 @@
         <v>84</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -24244,31 +24256,31 @@
         <v>84</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="Z167" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF167" t="s" s="2">
         <v>921</v>
-      </c>
-      <c r="AA167" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB167" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC167" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD167" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE167" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF167" t="s" s="2">
-        <v>917</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>82</v>
@@ -24295,24 +24307,24 @@
         <v>84</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="AQ167" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR167" t="s" s="2">
-        <v>924</v>
+        <v>928</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24335,13 +24347,13 @@
         <v>84</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -24392,7 +24404,7 @@
         <v>84</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -24416,13 +24428,13 @@
         <v>84</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="AQ168" t="s" s="2">
         <v>84</v>
@@ -24433,14 +24445,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -24459,16 +24471,16 @@
         <v>84</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -24518,7 +24530,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>82</v>
@@ -24548,7 +24560,7 @@
         <v>84</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>84</v>
@@ -24559,10 +24571,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24585,16 +24597,16 @@
         <v>84</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -24644,7 +24656,7 @@
         <v>84</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>82</v>
@@ -24668,13 +24680,13 @@
         <v>84</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="AQ170" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (52) to us-core-medicationrequest</t>
+    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (52) to us-core-medicationrequest.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6932" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6932" uniqueCount="958">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -612,10 +612,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mro-27-1746-1:undefined: if P then http://va.gov/terminology/vistaDefinedTerms/52-100 {null}</t>
-  </si>
-  <si>
-    <t>1746-1: fixed value = http://va.gov/terminology/vistaDefinedTerms/52-100 case P</t>
+mro-27-1746-1:If (undefined) is P then fixed value http://va.gov/terminology/vistaDefinedTerms/52-100 {null}</t>
+  </si>
+  <si>
+    <t>1746-1: fixed value = http://va.gov/terminology/vistaDefinedTerms/52-100 if P</t>
   </si>
   <si>
     <t>./codeSystem</t>
@@ -667,10 +667,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mro-27-1746:52-11: if P then #active-parked {null}</t>
-  </si>
-  <si>
-    <t>1746: fixed value = #active-parked when PRESCRIPTION - MAIL/WINDOW/PARK (52-11) case P</t>
+mro-27-1746:If (52-11) is P then fixed value #active-parked {null}</t>
+  </si>
+  <si>
+    <t>1746: fixed value = #active-parked when PRESCRIPTION - MAIL/WINDOW/PARK (52-11) if P</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.RxStatus</t>
@@ -772,7 +772,7 @@
 </t>
   </si>
   <si>
-    <t>1704: source value from PRESCRIPTION - CANCEL DATE (52-26.1)</t>
+    <t>1704: source value based on PRESCRIPTION - CANCEL DATE (52-26.1)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.CancelDate</t>
@@ -969,7 +969,7 @@
     <t>This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
-    <t>1664: source value from PRESCRIPTION - RX # (52-.01)</t>
+    <t>1664: source value based on PRESCRIPTION - RX # (52-.01)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.RxNumber</t>
@@ -1396,7 +1396,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>803: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY &gt; VA PRODUCT - VA PRINT NAME (52-6 &gt; 50-22 &gt; 50.68-5)</t>
+    <t>803: source value based on PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY &gt; VA PRODUCT - VA PRINT NAME (52-6 &gt; 50-22 &gt; 50.68-5)</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -1434,7 +1434,7 @@
     <t>The subject on a medication request is mandatory.  For the secondary use case where the actual subject is not provided, there still must be an anonymized subject specified.</t>
   </si>
   <si>
-    <t>806: reference from PRESCRIPTION - PATIENT (52-2)</t>
+    <t>806: reference based on PRESCRIPTION - PATIENT (52-2)</t>
   </si>
   <si>
     <t>RxOut.ActivityLog.PatientIEN,RxOut.ActivityLogOtherComments.PatientIEN,RxOut.RxOutpat.PatientIEN,RxOut.RxOutpatExt.PatientIEN,RxOut.RxOutpatExt.PatientSID,RxOut.RxOutpatFill.PatientIEN,RxOut.RxOutpatMedInstructions.PatientIEN,RxOut.RxOutpatSig.PatientIEN</t>
@@ -1516,7 +1516,7 @@
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
   </si>
   <si>
-    <t>807: source value from PRESCRIPTION - ISSUE DATE (52-1)</t>
+    <t>807: source value based on PRESCRIPTION - ISSUE DATE (52-1)</t>
   </si>
   <si>
     <t>RxOut.ActivityLog.IssueDateTime,RxOut.RxOutpat.IssueDate,RxOut.RxOutpatExt.IssueDateTime,RxOut.RxOutpatFill.IssueDate,RxOut.RxOutpatMedInstructions.IssueDate,RxOut.RxOutpatSig.IssueDate</t>
@@ -1553,7 +1553,7 @@
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
   </si>
   <si>
-    <t>808: reference from PRESCRIPTION - PROVIDER (52-4)</t>
+    <t>808: reference based on PRESCRIPTION - PROVIDER (52-4)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.ProviderIEN</t>
@@ -1678,7 +1678,7 @@
     <t>MedicationRequest.reasonCode.text</t>
   </si>
   <si>
-    <t>1705: source value from PRESCRIPTION - INDICATION FOR USE (52-128)</t>
+    <t>1705: source value based on PRESCRIPTION - INDICATION FOR USE (52-128)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatExt.IndicationForUse</t>
@@ -1917,7 +1917,7 @@
     <t>Dosage.text</t>
   </si>
   <si>
-    <t>809: source value from PRESCRIPTION - SIG (52-10)</t>
+    <t>809: source value based on PRESCRIPTION - SIG (52-10)</t>
   </si>
   <si>
     <t>RXO-6; RXE-21</t>
@@ -1962,7 +1962,7 @@
     <t>Dosage.patientInstruction</t>
   </si>
   <si>
-    <t>810: source value from PRESCRIPTION - PATIENT INSTRUCTIONS (52-114)</t>
+    <t>810: source value based on PRESCRIPTION - PATIENT INSTRUCTIONS (52-114)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatSig.PatientInstructions</t>
@@ -2114,7 +2114,7 @@
     <t>MedicationRequest.dosageInstruction.route.coding.code</t>
   </si>
   <si>
-    <t>1665: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - ROUTE (52-113 &gt; 52.0113-6)</t>
+    <t>1665: source value based on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - ROUTE (52-113 &gt; 52.0113-6)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.MedRoute</t>
@@ -2238,7 +2238,11 @@
 url</t>
   </si>
   <si>
-    <t>841: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) case not a number</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+mro-27-841:If not a number then source value from (52-113 &gt; 52.0113-.01) {null}</t>
+  </si>
+  <si>
+    <t>841: source value based on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) if not a number</t>
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.DoseOrdered</t>
@@ -2340,7 +2344,11 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>811: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) case number</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+mro-27-811:If number then source value from (52-113 &gt; 52.0113-.01) {null}</t>
+  </si>
+  <si>
+    <t>811: source value based on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) if number</t>
   </si>
   <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
@@ -2400,7 +2408,7 @@
     <t>Quantity.unit</t>
   </si>
   <si>
-    <t>812: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (52-113 &gt; 52.0113-2)</t>
+    <t>812: source value based on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - UNITS (52-113 &gt; 52.0113-2)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.Unit</t>
@@ -2718,7 +2726,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>815: source value from PRESCRIPTION - EXPIRATION DATE (52-26)</t>
+    <t>815: source value based on PRESCRIPTION - EXPIRATION DATE (52-26)</t>
   </si>
   <si>
     <t>Medication.ToTime,Medication.Expires</t>
@@ -2746,7 +2754,7 @@
     <t>If displaying "number of authorized fills", add 1 to this number.</t>
   </si>
   <si>
-    <t>816: source value from PRESCRIPTION - # OF REFILLS (52-9)</t>
+    <t>816: source value based on PRESCRIPTION - # OF REFILLS (52-9)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.MaxRefills</t>
@@ -2791,7 +2799,7 @@
     <t>MedicationRequest.dispenseRequest.quantity.value</t>
   </si>
   <si>
-    <t>1669: source value from PRESCRIPTION - QTY (52-7)</t>
+    <t>1669: source value based on PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
     <t>Medication.OrderQuantity</t>
@@ -2821,7 +2829,7 @@
     <t>In some situations, this attribute may be used instead of quantity to identify the amount supplied by how long it is expected to last, rather than the physical quantity issued, e.g. 90 days supply of medication (based on an ordered dosage). When possible, it is always better to specify quantity, as this tends to be more precise. expectedSupplyDuration will always be an estimate that can be influenced by external factors.</t>
   </si>
   <si>
-    <t>1670: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
+    <t>1670: source value based on PRESCRIPTION - DAYS SUPPLY (52-8)</t>
   </si>
   <si>
     <t>Medication.DaysSupply</t>
@@ -18766,13 +18774,13 @@
         <v>279</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>106</v>
+        <v>713</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>675</v>
@@ -18795,10 +18803,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18824,14 +18832,14 @@
         <v>326</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -18859,10 +18867,10 @@
         <v>330</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>84</v>
@@ -18880,7 +18888,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18916,15 +18924,15 @@
         <v>84</v>
       </c>
       <c r="AR124" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18947,19 +18955,19 @@
         <v>94</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
@@ -19006,7 +19014,7 @@
         <v>143</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -19042,18 +19050,18 @@
         <v>84</v>
       </c>
       <c r="AR125" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>84</v>
@@ -19075,19 +19083,19 @@
         <v>94</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -19136,7 +19144,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -19172,15 +19180,15 @@
         <v>84</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19301,10 +19309,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19427,10 +19435,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19453,19 +19461,19 @@
         <v>94</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19514,7 +19522,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19526,13 +19534,13 @@
         <v>84</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>106</v>
+        <v>747</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>675</v>
@@ -19544,21 +19552,21 @@
         <v>84</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR129" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19584,20 +19592,20 @@
         <v>114</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q130" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="R130" t="s" s="2">
         <v>84</v>
@@ -19621,10 +19629,10 @@
         <v>318</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>84</v>
@@ -19642,7 +19650,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19672,21 +19680,21 @@
         <v>84</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR130" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19712,14 +19720,14 @@
         <v>153</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>84</v>
@@ -19768,7 +19776,7 @@
         <v>84</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>82</v>
@@ -19783,10 +19791,10 @@
         <v>106</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>675</v>
@@ -19798,21 +19806,21 @@
         <v>84</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="AQ131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR131" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19838,14 +19846,14 @@
         <v>108</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
@@ -19894,7 +19902,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -19903,7 +19911,7 @@
         <v>93</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>106</v>
@@ -19924,21 +19932,21 @@
         <v>84</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR132" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19964,16 +19972,16 @@
         <v>114</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
@@ -20022,7 +20030,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -20052,21 +20060,21 @@
         <v>84</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR133" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20089,19 +20097,19 @@
         <v>94</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -20150,7 +20158,7 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
@@ -20180,21 +20188,21 @@
         <v>84</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR134" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20217,19 +20225,19 @@
         <v>94</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>84</v>
@@ -20278,7 +20286,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -20308,21 +20316,21 @@
         <v>84</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR135" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20345,19 +20353,19 @@
         <v>94</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>84</v>
@@ -20406,7 +20414,7 @@
         <v>84</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>82</v>
@@ -20436,7 +20444,7 @@
         <v>84</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="AQ136" t="s" s="2">
         <v>84</v>
@@ -20447,10 +20455,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20473,17 +20481,17 @@
         <v>94</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>84</v>
@@ -20532,7 +20540,7 @@
         <v>84</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>82</v>
@@ -20562,7 +20570,7 @@
         <v>84</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="AQ137" t="s" s="2">
         <v>84</v>
@@ -20573,10 +20581,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20599,13 +20607,13 @@
         <v>84</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -20656,7 +20664,7 @@
         <v>84</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>82</v>
@@ -20683,10 +20691,10 @@
         <v>84</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="AQ138" t="s" s="2">
         <v>84</v>
@@ -20697,10 +20705,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20821,10 +20829,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20947,10 +20955,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21075,10 +21083,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -21101,16 +21109,16 @@
         <v>84</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -21160,7 +21168,7 @@
         <v>84</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>82</v>
@@ -21190,7 +21198,7 @@
         <v>84</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="AQ142" t="s" s="2">
         <v>84</v>
@@ -21201,10 +21209,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21325,10 +21333,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21451,10 +21459,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21579,10 +21587,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21605,13 +21613,13 @@
         <v>84</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -21662,7 +21670,7 @@
         <v>84</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>82</v>
@@ -21692,7 +21700,7 @@
         <v>84</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="AQ146" t="s" s="2">
         <v>84</v>
@@ -21703,10 +21711,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21729,13 +21737,13 @@
         <v>84</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -21786,7 +21794,7 @@
         <v>84</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>82</v>
@@ -21816,7 +21824,7 @@
         <v>84</v>
       </c>
       <c r="AP147" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="AQ147" t="s" s="2">
         <v>84</v>
@@ -21827,10 +21835,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21853,13 +21861,13 @@
         <v>84</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -21910,7 +21918,7 @@
         <v>84</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>82</v>
@@ -21940,7 +21948,7 @@
         <v>84</v>
       </c>
       <c r="AP148" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="AQ148" t="s" s="2">
         <v>84</v>
@@ -21951,10 +21959,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21977,19 +21985,19 @@
         <v>84</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>84</v>
@@ -22038,7 +22046,7 @@
         <v>84</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>82</v>
@@ -22065,10 +22073,10 @@
         <v>84</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="AQ149" t="s" s="2">
         <v>84</v>
@@ -22079,10 +22087,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22203,10 +22211,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22329,10 +22337,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22358,13 +22366,13 @@
         <v>242</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -22414,7 +22422,7 @@
         <v>84</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>82</v>
@@ -22423,7 +22431,7 @@
         <v>93</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>106</v>
@@ -22444,21 +22452,21 @@
         <v>84</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR152" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22484,20 +22492,20 @@
         <v>242</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q153" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="R153" t="s" s="2">
         <v>84</v>
@@ -22542,7 +22550,7 @@
         <v>84</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>82</v>
@@ -22551,19 +22559,19 @@
         <v>93</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="AJ153" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>84</v>
@@ -22572,21 +22580,21 @@
         <v>84</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="AQ153" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR153" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22609,16 +22617,16 @@
         <v>84</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -22668,7 +22676,7 @@
         <v>84</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>82</v>
@@ -22683,36 +22691,36 @@
         <v>106</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="AQ154" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR154" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22735,13 +22743,13 @@
         <v>84</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -22792,7 +22800,7 @@
         <v>84</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>82</v>
@@ -22819,24 +22827,24 @@
         <v>84</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AQ155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR155" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22957,10 +22965,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23083,10 +23091,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23109,19 +23117,19 @@
         <v>94</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>84</v>
@@ -23170,7 +23178,7 @@
         <v>84</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>82</v>
@@ -23185,13 +23193,13 @@
         <v>106</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>84</v>
@@ -23200,21 +23208,21 @@
         <v>84</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AQ158" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR158" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23240,20 +23248,20 @@
         <v>114</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q159" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="R159" t="s" s="2">
         <v>84</v>
@@ -23277,10 +23285,10 @@
         <v>318</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>84</v>
@@ -23298,7 +23306,7 @@
         <v>84</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>82</v>
@@ -23328,21 +23336,21 @@
         <v>84</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AQ159" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR159" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23368,14 +23376,14 @@
         <v>153</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>84</v>
@@ -23424,7 +23432,7 @@
         <v>84</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
@@ -23454,21 +23462,21 @@
         <v>84</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="AQ160" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR160" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23494,14 +23502,14 @@
         <v>108</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>84</v>
@@ -23550,7 +23558,7 @@
         <v>84</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>82</v>
@@ -23559,7 +23567,7 @@
         <v>93</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>106</v>
@@ -23580,21 +23588,21 @@
         <v>84</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="AQ161" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR161" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23620,16 +23628,16 @@
         <v>114</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>84</v>
@@ -23678,7 +23686,7 @@
         <v>84</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23708,21 +23716,21 @@
         <v>84</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR162" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23745,16 +23753,16 @@
         <v>84</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -23804,7 +23812,7 @@
         <v>84</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>82</v>
@@ -23819,22 +23827,22 @@
         <v>106</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="AQ163" t="s" s="2">
         <v>84</v>
@@ -23845,10 +23853,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23871,13 +23879,13 @@
         <v>84</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -23928,7 +23936,7 @@
         <v>84</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>82</v>
@@ -23958,7 +23966,7 @@
         <v>84</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="AQ164" t="s" s="2">
         <v>515</v>
@@ -23969,10 +23977,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23995,13 +24003,13 @@
         <v>84</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -24052,7 +24060,7 @@
         <v>84</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>82</v>
@@ -24079,10 +24087,10 @@
         <v>84</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="AQ165" t="s" s="2">
         <v>84</v>
@@ -24093,10 +24101,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24217,10 +24225,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24343,10 +24351,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24471,10 +24479,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24500,13 +24508,13 @@
         <v>635</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -24535,10 +24543,10 @@
         <v>330</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>84</v>
@@ -24556,7 +24564,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>93</v>
@@ -24583,24 +24591,24 @@
         <v>84</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR169" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24626,10 +24634,10 @@
         <v>326</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -24659,10 +24667,10 @@
         <v>330</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>84</v>
@@ -24680,7 +24688,7 @@
         <v>84</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>82</v>
@@ -24707,24 +24715,24 @@
         <v>84</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="AQ170" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR170" t="s" s="2">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24747,13 +24755,13 @@
         <v>84</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -24804,7 +24812,7 @@
         <v>84</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>82</v>
@@ -24828,13 +24836,13 @@
         <v>84</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="AP171" t="s" s="2">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="AQ171" t="s" s="2">
         <v>84</v>
@@ -24845,14 +24853,14 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
@@ -24871,16 +24879,16 @@
         <v>84</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -24930,7 +24938,7 @@
         <v>84</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>82</v>
@@ -24960,7 +24968,7 @@
         <v>84</v>
       </c>
       <c r="AP172" t="s" s="2">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="AQ172" t="s" s="2">
         <v>84</v>
@@ -24971,10 +24979,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -24997,16 +25005,16 @@
         <v>84</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -25056,7 +25064,7 @@
         <v>84</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>82</v>
@@ -25080,13 +25088,13 @@
         <v>84</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP173" t="s" s="2">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="AQ173" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6932" uniqueCount="958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6941" uniqueCount="986">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -809,97 +809,13 @@
     <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x]</t>
   </si>
   <si>
+    <t>see mapping [VF_Boolean](ConceptMap-VF-Boolean.html)</t>
+  </si>
+  <si>
     <t>1706: transform using VF_Boolean on PRESCRIPTION - INDICATION FOR USE FLAG (52-129)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatExt.IndicationForUseFlag</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x].id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x].extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x].extension:11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t>11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {11179-permitted-value-conceptmap}
-</t>
-  </si>
-  <si>
-    <t>Mapping from permitted to transmitted</t>
-  </si>
-  <si>
-    <t>Expresses the linkage between the internal codes used for storage and the codes used for exchange.</t>
-  </si>
-  <si>
-    <t>The permitted value set must have a 1..1 set of codes for each code in the value meaning value set.  The source for the concept map is the value set the extension appears on.  The target is the permitted-value-valueset.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x].extension:11179-permitted-value-conceptmap.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension.value[x].extension.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x].extension:11179-permitted-value-conceptmap.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension.value[x].extension.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x].extension:11179-permitted-value-conceptmap.url</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension.value[x].extension.url</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x].extension:11179-permitted-value-conceptmap.value[x]</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension.value[x].extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(ConceptMap)
-</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ConceptMap/VF-Boolean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x].value</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension.value[x].value</t>
-  </si>
-  <si>
-    <t>Primitive value for boolean</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>boolean.value</t>
   </si>
   <si>
     <t>MedicationRequest.extension:medicationrequest-remainingRefillCount</t>
@@ -969,15 +885,6 @@
     <t>This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
-    <t>1664: source value based on PRESCRIPTION - RX # (52-.01)</t>
-  </si>
-  <si>
-    <t>RxOut.RxOutpat.RxNumber</t>
-  </si>
-  <si>
-    <t>Medication.PrescriptionNumber,Medication.FillDate</t>
-  </si>
-  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -993,44 +900,228 @@
     <t>ORC-2-Placer Order Number / ORC-3-Filler Order Number</t>
   </si>
   <si>
-    <t>MedicationRequest.status</t>
-  </si>
-  <si>
-    <t>active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown</t>
-  </si>
-  <si>
-    <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+    <t>MedicationRequest.identifier.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/OutMedRequestStatus</t>
-  </si>
-  <si>
-    <t>799: terminologyMaps using VF_OutMedRequestStatus on PRESCRIPTION - STATUS (52-100)</t>
-  </si>
-  <si>
-    <t>Request.status</t>
-  </si>
-  <si>
-    <t>no mapping</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>MedicationRequest.statusReason</t>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier.type</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0203"/&gt;
+    &lt;code value="FILL"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>1664-1: fixed value = http://terminology.hl7.org/CodeSystem/v2-0203#FILL</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>1664: source value based on PRESCRIPTION - RX # (52-.01)</t>
+  </si>
+  <si>
+    <t>RxOut.RxOutpat.RxNumber</t>
+  </si>
+  <si>
+    <t>Medication.PrescriptionNumber,Medication.FillDate</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>MedicationRequest.status</t>
+  </si>
+  <si>
+    <t>active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown</t>
+  </si>
+  <si>
+    <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_OutMedRequestStatus](ConceptMap-VF-OutMedRequestStatus.html)</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/OutMedRequestStatus</t>
+  </si>
+  <si>
+    <t>799: terminologyMaps using VF_OutMedRequestStatus on PRESCRIPTION - STATUS (52-100)</t>
+  </si>
+  <si>
+    <t>Request.status</t>
+  </si>
+  <si>
+    <t>no mapping</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>MedicationRequest.statusReason</t>
   </si>
   <si>
     <t>Reason for current status</t>
@@ -1244,9 +1335,6 @@
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the Medication resource is recommended.  For example, if you require form or lot number or if the medication is compounded or extemporaneously prepared, then you must reference the Medication resource.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.4</t>
@@ -2238,6 +2326,13 @@
 url</t>
   </si>
   <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 mro-27-841:If not a number then source value from (52-113 &gt; 52.0113-.01) {null}</t>
   </si>
@@ -2655,10 +2750,6 @@
     <t>MedicationRequest.dispenseRequest.validityPeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
     <t>Time period supply is authorized for</t>
   </si>
   <si>
@@ -2842,10 +2933,6 @@
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
   </si>
   <si>
     <t>Intended dispenser</t>
@@ -3310,7 +3397,7 @@
   <dimension ref="A1:AR173"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="127.9765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="87.59375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="67.53125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="39.234375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -3329,7 +3416,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
@@ -7159,7 +7246,9 @@
       <c r="M31" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="N31" s="2"/>
+      <c r="N31" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -7223,10 +7312,10 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>84</v>
@@ -7249,12 +7338,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="D32" t="s" s="2">
         <v>84</v>
       </c>
@@ -7275,13 +7366,13 @@
         <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>153</v>
+        <v>260</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>258</v>
+        <v>140</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -7332,19 +7423,19 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>84</v>
@@ -7373,10 +7464,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7387,7 +7478,7 @@
         <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>84</v>
@@ -7399,13 +7490,13 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -7444,29 +7535,31 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
@@ -7484,7 +7577,7 @@
         <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -7495,14 +7588,12 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>84</v>
       </c>
@@ -7511,7 +7602,7 @@
         <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>84</v>
@@ -7523,17 +7614,15 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>263</v>
+        <v>139</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>264</v>
+        <v>140</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -7570,16 +7659,16 @@
         <v>84</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>161</v>
@@ -7612,21 +7701,21 @@
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>268</v>
+        <v>163</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7634,7 +7723,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
@@ -7649,22 +7738,24 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>84</v>
@@ -7706,16 +7797,16 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>84</v>
@@ -7736,7 +7827,7 @@
         <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -7747,10 +7838,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>270</v>
+        <v>170</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7761,10 +7852,10 @@
         <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
@@ -7773,13 +7864,13 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>139</v>
+        <v>267</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>141</v>
+        <v>173</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7818,34 +7909,34 @@
         <v>84</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>84</v>
+        <v>268</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
@@ -7860,7 +7951,7 @@
         <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -7871,104 +7962,106 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="S37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="AG37" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -8000,7 +8093,7 @@
         <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -8008,10 +8101,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>84</v>
@@ -8023,15 +8116,17 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="M38" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="N38" s="2"/>
+      <c r="N38" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -8041,7 +8136,7 @@
         <v>84</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>84</v>
@@ -8080,16 +8175,16 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>174</v>
+        <v>274</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>279</v>
+        <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -8104,27 +8199,27 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>137</v>
+        <v>281</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>84</v>
+        <v>282</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -8147,13 +8242,13 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>225</v>
+        <v>153</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>282</v>
+        <v>154</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>283</v>
+        <v>155</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -8204,7 +8299,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>284</v>
+        <v>156</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -8234,7 +8329,7 @@
         <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -8248,20 +8343,18 @@
         <v>285</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>84</v>
@@ -8273,15 +8366,17 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>287</v>
+        <v>139</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -8318,19 +8413,19 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -8339,7 +8434,7 @@
         <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>145</v>
@@ -8360,7 +8455,7 @@
         <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -8371,10 +8466,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>152</v>
+        <v>286</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8391,22 +8486,26 @@
         <v>84</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>154</v>
+        <v>287</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
       </c>
@@ -8430,13 +8529,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -8454,7 +8553,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>156</v>
+        <v>294</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -8466,7 +8565,7 @@
         <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>84</v>
@@ -8484,21 +8583,21 @@
         <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>157</v>
+        <v>295</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>84</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>159</v>
+        <v>296</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8509,28 +8608,32 @@
         <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>139</v>
+        <v>297</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>140</v>
+        <v>298</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -8539,7 +8642,7 @@
         <v>84</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>84</v>
+        <v>302</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>84</v>
@@ -8554,46 +8657,46 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>84</v>
+        <v>304</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>84</v>
+        <v>305</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>161</v>
+        <v>306</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>84</v>
@@ -8608,21 +8711,21 @@
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>84</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8630,7 +8733,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -8642,33 +8745,35 @@
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>164</v>
+        <v>310</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>165</v>
+        <v>311</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>84</v>
+        <v>314</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>84</v>
@@ -8704,10 +8809,10 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>168</v>
+        <v>315</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>93</v>
@@ -8716,7 +8821,7 @@
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -8734,21 +8839,21 @@
         <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>137</v>
+        <v>316</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>84</v>
+        <v>317</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>170</v>
+        <v>318</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8768,18 +8873,20 @@
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>294</v>
+        <v>153</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>172</v>
+        <v>319</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8792,7 +8899,7 @@
         <v>84</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>84</v>
@@ -8828,7 +8935,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>174</v>
+        <v>323</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8843,13 +8950,13 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>84</v>
+        <v>325</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>84</v>
+        <v>326</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>84</v>
@@ -8858,57 +8965,53 @@
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>137</v>
+        <v>327</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>84</v>
+        <v>328</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>296</v>
+        <v>329</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>296</v>
+        <v>329</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J45" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="J45" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K45" t="s" s="2">
-        <v>139</v>
+        <v>330</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -8956,19 +9059,19 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -8986,21 +9089,21 @@
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>137</v>
+        <v>334</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>84</v>
+        <v>335</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -9011,28 +9114,28 @@
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J46" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K46" t="s" s="2">
-        <v>302</v>
+        <v>337</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>303</v>
+        <v>338</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>305</v>
+        <v>340</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -9082,13 +9185,13 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>84</v>
@@ -9097,36 +9200,36 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>306</v>
+        <v>84</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>307</v>
+        <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>308</v>
+        <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>309</v>
+        <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>310</v>
+        <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>311</v>
+        <v>342</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>313</v>
+        <v>343</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -9152,13 +9255,13 @@
         <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -9184,11 +9287,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -9206,7 +9311,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>93</v>
@@ -9221,7 +9326,7 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>211</v>
@@ -9230,16 +9335,16 @@
         <v>212</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -9247,10 +9352,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9273,16 +9378,16 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>329</v>
+        <v>358</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -9308,13 +9413,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>332</v>
+        <v>361</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -9332,7 +9437,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -9356,13 +9461,13 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -9373,10 +9478,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9402,13 +9507,13 @@
         <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -9419,7 +9524,7 @@
         <v>84</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>84</v>
@@ -9434,13 +9539,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -9458,7 +9563,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>93</v>
@@ -9473,7 +9578,7 @@
         <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>84</v>
@@ -9482,16 +9587,16 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -9499,10 +9604,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9525,16 +9630,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -9545,7 +9650,7 @@
         <v>84</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>84</v>
@@ -9560,19 +9665,19 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -9582,7 +9687,7 @@
         <v>143</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9597,7 +9702,7 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>84</v>
@@ -9609,13 +9714,13 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>356</v>
+        <v>385</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -9623,13 +9728,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>84</v>
@@ -9651,16 +9756,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9686,13 +9791,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -9710,7 +9815,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9737,13 +9842,13 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>356</v>
+        <v>385</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9751,10 +9856,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9780,10 +9885,10 @@
         <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9810,13 +9915,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>363</v>
+        <v>392</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>364</v>
+        <v>393</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -9834,7 +9939,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9858,16 +9963,16 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>365</v>
+        <v>394</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>366</v>
+        <v>395</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>367</v>
+        <v>396</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9875,10 +9980,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>368</v>
+        <v>397</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>368</v>
+        <v>397</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9904,13 +10009,13 @@
         <v>225</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>371</v>
+        <v>400</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9960,7 +10065,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>368</v>
+        <v>397</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9990,7 +10095,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -10001,10 +10106,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>373</v>
+        <v>402</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>373</v>
+        <v>402</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -10027,13 +10132,13 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -10072,17 +10177,17 @@
         <v>84</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>373</v>
+        <v>402</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -10112,7 +10217,7 @@
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -10123,13 +10228,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>373</v>
+        <v>402</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>381</v>
+        <v>410</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>84</v>
@@ -10154,10 +10259,10 @@
         <v>225</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -10208,7 +10313,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>373</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -10223,7 +10328,7 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>382</v>
+        <v>411</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>84</v>
@@ -10238,7 +10343,7 @@
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -10249,13 +10354,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>383</v>
+        <v>412</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>373</v>
+        <v>402</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>84</v>
@@ -10277,13 +10382,13 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>385</v>
+        <v>414</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -10334,7 +10439,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>373</v>
+        <v>402</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -10349,7 +10454,7 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>84</v>
@@ -10364,7 +10469,7 @@
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -10375,10 +10480,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10401,16 +10506,16 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10436,27 +10541,27 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>392</v>
+        <v>303</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>93</v>
@@ -10480,30 +10585,30 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>398</v>
+        <v>426</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>84</v>
@@ -10525,16 +10630,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10560,11 +10665,11 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>392</v>
+        <v>303</v>
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -10582,7 +10687,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>93</v>
@@ -10606,27 +10711,27 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>398</v>
+        <v>426</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10747,10 +10852,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10873,10 +10978,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10902,16 +11007,16 @@
         <v>171</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10960,7 +11065,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10990,21 +11095,21 @@
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>413</v>
+        <v>441</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -11125,10 +11230,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11251,10 +11356,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11299,7 +11404,7 @@
         <v>84</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>84</v>
@@ -11353,7 +11458,7 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>84</v>
@@ -11379,10 +11484,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11505,10 +11610,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11605,13 +11710,13 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>84</v>
@@ -11631,10 +11736,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11757,10 +11862,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11885,10 +11990,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11914,16 +12019,16 @@
         <v>153</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -11972,7 +12077,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11987,13 +12092,13 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>84</v>
@@ -12002,24 +12107,24 @@
         <v>84</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>442</v>
+        <v>470</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>443</v>
+        <v>471</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>84</v>
@@ -12041,16 +12146,16 @@
         <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -12100,7 +12205,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>93</v>
@@ -12115,7 +12220,7 @@
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>84</v>
@@ -12124,27 +12229,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>398</v>
+        <v>426</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12167,16 +12272,16 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>450</v>
+        <v>478</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -12226,7 +12331,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>93</v>
@@ -12241,36 +12346,36 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>458</v>
+        <v>486</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>459</v>
+        <v>487</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>459</v>
+        <v>487</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12293,16 +12398,16 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>460</v>
+        <v>488</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>461</v>
+        <v>489</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>462</v>
+        <v>490</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -12352,7 +12457,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>459</v>
+        <v>487</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -12367,7 +12472,7 @@
         <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>84</v>
@@ -12376,27 +12481,27 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>467</v>
+        <v>495</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>468</v>
+        <v>496</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>469</v>
+        <v>497</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>469</v>
+        <v>497</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12419,13 +12524,13 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>470</v>
+        <v>498</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>472</v>
+        <v>500</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -12476,7 +12581,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>469</v>
+        <v>497</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -12500,16 +12605,16 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>473</v>
+        <v>501</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>474</v>
+        <v>502</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>467</v>
+        <v>495</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>84</v>
@@ -12517,10 +12622,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>475</v>
+        <v>503</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>475</v>
+        <v>503</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12546,10 +12651,10 @@
         <v>242</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>476</v>
+        <v>504</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>477</v>
+        <v>505</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -12600,7 +12705,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>475</v>
+        <v>503</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12615,36 +12720,36 @@
         <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>478</v>
+        <v>506</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>479</v>
+        <v>507</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>480</v>
+        <v>508</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>481</v>
+        <v>509</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>482</v>
+        <v>510</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>483</v>
+        <v>511</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>484</v>
+        <v>512</v>
       </c>
       <c r="AR74" t="s" s="2">
-        <v>485</v>
+        <v>513</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>486</v>
+        <v>514</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>486</v>
+        <v>514</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12667,13 +12772,13 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>488</v>
+        <v>516</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>489</v>
+        <v>517</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -12724,7 +12829,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>486</v>
+        <v>514</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12739,25 +12844,25 @@
         <v>106</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>490</v>
+        <v>518</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>491</v>
+        <v>519</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>492</v>
+        <v>520</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>493</v>
+        <v>521</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>494</v>
+        <v>522</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>84</v>
@@ -12765,10 +12870,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>495</v>
+        <v>523</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>495</v>
+        <v>523</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12791,13 +12896,13 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>496</v>
+        <v>524</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>497</v>
+        <v>525</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12848,7 +12953,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>495</v>
+        <v>523</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12872,16 +12977,16 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>499</v>
+        <v>527</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>500</v>
+        <v>528</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>84</v>
@@ -12889,10 +12994,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>502</v>
+        <v>530</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>502</v>
+        <v>530</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12915,16 +13020,16 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>503</v>
+        <v>531</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>504</v>
+        <v>532</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>505</v>
+        <v>533</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12950,13 +13055,13 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>507</v>
+        <v>535</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -12974,7 +13079,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>502</v>
+        <v>530</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12998,13 +13103,13 @@
         <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>508</v>
+        <v>536</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -13015,10 +13120,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>510</v>
+        <v>538</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>510</v>
+        <v>538</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13041,13 +13146,13 @@
         <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>512</v>
+        <v>540</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -13098,7 +13203,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>510</v>
+        <v>538</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -13128,10 +13233,10 @@
         <v>84</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>514</v>
+        <v>542</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>84</v>
@@ -13139,10 +13244,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>516</v>
+        <v>544</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>516</v>
+        <v>544</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13165,16 +13270,16 @@
         <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>517</v>
+        <v>545</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>518</v>
+        <v>546</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -13200,13 +13305,13 @@
         <v>84</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>520</v>
+        <v>548</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -13224,7 +13329,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>516</v>
+        <v>544</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -13248,27 +13353,27 @@
         <v>84</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>524</v>
+        <v>552</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>525</v>
+        <v>553</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>526</v>
+        <v>554</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>527</v>
+        <v>555</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>527</v>
+        <v>555</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13389,10 +13494,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13515,10 +13620,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>529</v>
+        <v>557</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>529</v>
+        <v>557</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13544,16 +13649,16 @@
         <v>171</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -13602,7 +13707,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13632,21 +13737,21 @@
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>413</v>
+        <v>441</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13672,16 +13777,16 @@
         <v>153</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -13730,7 +13835,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13745,13 +13850,13 @@
         <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>531</v>
+        <v>559</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>532</v>
+        <v>560</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>533</v>
+        <v>561</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>84</v>
@@ -13760,21 +13865,21 @@
         <v>84</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>442</v>
+        <v>470</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>534</v>
+        <v>562</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>534</v>
+        <v>562</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13797,16 +13902,16 @@
         <v>84</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>535</v>
+        <v>563</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>538</v>
+        <v>566</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13856,7 +13961,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>534</v>
+        <v>562</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13880,16 +13985,16 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>539</v>
+        <v>567</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>540</v>
+        <v>568</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>525</v>
+        <v>553</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>84</v>
@@ -13897,10 +14002,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>541</v>
+        <v>569</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>541</v>
+        <v>569</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13923,13 +14028,13 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>544</v>
+        <v>572</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13980,7 +14085,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>541</v>
+        <v>569</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -14004,13 +14109,13 @@
         <v>84</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>545</v>
+        <v>573</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>546</v>
+        <v>574</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -14021,10 +14126,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>547</v>
+        <v>575</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>547</v>
+        <v>575</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -14050,10 +14155,10 @@
         <v>108</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>548</v>
+        <v>576</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>549</v>
+        <v>577</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -14104,7 +14209,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>547</v>
+        <v>575</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -14134,7 +14239,7 @@
         <v>84</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>546</v>
+        <v>574</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -14145,10 +14250,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14171,13 +14276,13 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>551</v>
+        <v>579</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>552</v>
+        <v>580</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -14228,7 +14333,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -14252,13 +14357,13 @@
         <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -14269,10 +14374,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14295,17 +14400,17 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>558</v>
+        <v>586</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>559</v>
+        <v>587</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -14354,7 +14459,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -14378,13 +14483,13 @@
         <v>84</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>561</v>
+        <v>589</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -14395,10 +14500,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14421,16 +14526,16 @@
         <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>563</v>
+        <v>591</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -14456,13 +14561,13 @@
         <v>84</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>84</v>
@@ -14480,7 +14585,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14510,7 +14615,7 @@
         <v>84</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>568</v>
+        <v>596</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14521,10 +14626,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>569</v>
+        <v>597</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>569</v>
+        <v>597</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14547,13 +14652,13 @@
         <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>570</v>
+        <v>598</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>571</v>
+        <v>599</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>572</v>
+        <v>600</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -14604,7 +14709,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>569</v>
+        <v>597</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14628,13 +14733,13 @@
         <v>84</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14645,10 +14750,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14671,13 +14776,13 @@
         <v>84</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>576</v>
+        <v>604</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>577</v>
+        <v>605</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -14728,7 +14833,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14752,13 +14857,13 @@
         <v>84</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>579</v>
+        <v>607</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>580</v>
+        <v>608</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>581</v>
+        <v>609</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14769,10 +14874,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14795,16 +14900,16 @@
         <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>583</v>
+        <v>611</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>584</v>
+        <v>612</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>585</v>
+        <v>613</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>586</v>
+        <v>614</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -14854,7 +14959,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14878,13 +14983,13 @@
         <v>84</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>588</v>
+        <v>616</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14895,10 +15000,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>589</v>
+        <v>617</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>589</v>
+        <v>617</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -15019,10 +15124,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>590</v>
+        <v>618</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>590</v>
+        <v>618</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -15145,14 +15250,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>591</v>
+        <v>619</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>591</v>
+        <v>619</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -15174,16 +15279,16 @@
         <v>139</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -15232,7 +15337,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -15273,10 +15378,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15299,17 +15404,17 @@
         <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>294</v>
+        <v>267</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>598</v>
+        <v>626</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>599</v>
+        <v>627</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -15358,7 +15463,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>600</v>
+        <v>628</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -15388,21 +15493,21 @@
         <v>84</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>601</v>
+        <v>629</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>602</v>
+        <v>630</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>603</v>
+        <v>631</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>603</v>
+        <v>631</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15428,14 +15533,14 @@
         <v>153</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>604</v>
+        <v>632</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>606</v>
+        <v>634</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15484,7 +15589,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>607</v>
+        <v>635</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15499,7 +15604,7 @@
         <v>106</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>608</v>
+        <v>636</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>84</v>
@@ -15514,21 +15619,21 @@
         <v>84</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>601</v>
+        <v>629</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>609</v>
+        <v>637</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>610</v>
+        <v>638</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>610</v>
+        <v>638</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15551,19 +15656,19 @@
         <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>611</v>
+        <v>639</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>612</v>
+        <v>640</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>613</v>
+        <v>641</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>614</v>
+        <v>642</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>84</v>
@@ -15588,13 +15693,13 @@
         <v>84</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>616</v>
+        <v>644</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -15612,7 +15717,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>617</v>
+        <v>645</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15642,21 +15747,21 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>601</v>
+        <v>629</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>618</v>
+        <v>646</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>619</v>
+        <v>647</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>619</v>
+        <v>647</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15682,10 +15787,10 @@
         <v>153</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>620</v>
+        <v>648</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>621</v>
+        <v>649</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -15736,7 +15841,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>622</v>
+        <v>650</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15751,13 +15856,13 @@
         <v>106</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>623</v>
+        <v>651</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>624</v>
+        <v>652</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>625</v>
+        <v>653</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>84</v>
@@ -15766,21 +15871,21 @@
         <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>601</v>
+        <v>629</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>618</v>
+        <v>646</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>626</v>
+        <v>654</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>626</v>
+        <v>654</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15803,19 +15908,19 @@
         <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>627</v>
+        <v>655</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>629</v>
+        <v>657</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>630</v>
+        <v>658</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>631</v>
+        <v>659</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
@@ -15864,7 +15969,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>632</v>
+        <v>660</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15894,7 +15999,7 @@
         <v>84</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>633</v>
+        <v>661</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15905,10 +16010,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>634</v>
+        <v>662</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>634</v>
+        <v>662</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15931,16 +16036,16 @@
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>635</v>
+        <v>663</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>636</v>
+        <v>664</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>638</v>
+        <v>666</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15966,13 +16071,13 @@
         <v>84</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>639</v>
+        <v>667</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>640</v>
+        <v>668</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>84</v>
@@ -15990,7 +16095,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>641</v>
+        <v>669</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -16020,21 +16125,21 @@
         <v>84</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>642</v>
+        <v>670</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>643</v>
+        <v>671</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>644</v>
+        <v>672</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>644</v>
+        <v>672</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -16057,19 +16162,19 @@
         <v>94</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>645</v>
+        <v>673</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>647</v>
+        <v>675</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>648</v>
+        <v>676</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>84</v>
@@ -16094,13 +16199,13 @@
         <v>84</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>649</v>
+        <v>677</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>650</v>
+        <v>678</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>84</v>
@@ -16118,7 +16223,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>651</v>
+        <v>679</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -16148,21 +16253,21 @@
         <v>84</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>652</v>
+        <v>680</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR102" t="s" s="2">
-        <v>653</v>
+        <v>681</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>654</v>
+        <v>682</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>654</v>
+        <v>682</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16185,17 +16290,17 @@
         <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>655</v>
+        <v>683</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>656</v>
+        <v>684</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>657</v>
+        <v>685</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -16220,13 +16325,13 @@
         <v>84</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>658</v>
+        <v>686</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>659</v>
+        <v>687</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>84</v>
@@ -16244,7 +16349,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>660</v>
+        <v>688</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -16274,21 +16379,21 @@
         <v>84</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>661</v>
+        <v>689</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>662</v>
+        <v>690</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>663</v>
+        <v>691</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>663</v>
+        <v>691</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16409,10 +16514,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>664</v>
+        <v>692</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>664</v>
+        <v>692</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16535,10 +16640,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>665</v>
+        <v>693</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>665</v>
+        <v>693</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16564,16 +16669,16 @@
         <v>171</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>84</v>
@@ -16622,7 +16727,7 @@
         <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>82</v>
@@ -16652,21 +16757,21 @@
         <v>84</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR106" t="s" s="2">
-        <v>413</v>
+        <v>441</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>666</v>
+        <v>694</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>666</v>
+        <v>694</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16787,10 +16892,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>667</v>
+        <v>695</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>667</v>
+        <v>695</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16913,10 +17018,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>668</v>
+        <v>696</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>668</v>
+        <v>696</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16961,7 +17066,7 @@
         <v>84</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>669</v>
+        <v>697</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>84</v>
@@ -17015,7 +17120,7 @@
         <v>106</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>670</v>
+        <v>698</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>84</v>
@@ -17041,10 +17146,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>671</v>
+        <v>699</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>671</v>
+        <v>699</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17167,10 +17272,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>672</v>
+        <v>700</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>672</v>
+        <v>700</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17267,13 +17372,13 @@
         <v>106</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>673</v>
+        <v>701</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>674</v>
+        <v>702</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>675</v>
+        <v>703</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>84</v>
@@ -17293,10 +17398,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>676</v>
+        <v>704</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>676</v>
+        <v>704</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17419,10 +17524,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>677</v>
+        <v>705</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>677</v>
+        <v>705</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17547,10 +17652,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17576,16 +17681,16 @@
         <v>153</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>84</v>
@@ -17634,7 +17739,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17664,21 +17769,21 @@
         <v>84</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR114" t="s" s="2">
-        <v>442</v>
+        <v>470</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>679</v>
+        <v>707</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>679</v>
+        <v>707</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17701,19 +17806,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>680</v>
+        <v>708</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>681</v>
+        <v>709</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
@@ -17738,13 +17843,13 @@
         <v>84</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>684</v>
+        <v>712</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>685</v>
+        <v>713</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>84</v>
@@ -17762,7 +17867,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>686</v>
+        <v>714</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17792,21 +17897,21 @@
         <v>84</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>687</v>
+        <v>715</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR115" t="s" s="2">
-        <v>688</v>
+        <v>716</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>689</v>
+        <v>717</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>689</v>
+        <v>717</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17829,13 +17934,13 @@
         <v>94</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>690</v>
+        <v>718</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>691</v>
+        <v>719</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>692</v>
+        <v>720</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -17886,7 +17991,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>693</v>
+        <v>721</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17922,15 +18027,15 @@
         <v>84</v>
       </c>
       <c r="AR116" t="s" s="2">
-        <v>694</v>
+        <v>722</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>695</v>
+        <v>723</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>695</v>
+        <v>723</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -18051,10 +18156,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>696</v>
+        <v>724</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>696</v>
+        <v>724</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18177,13 +18282,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>697</v>
+        <v>725</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>696</v>
+        <v>724</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>698</v>
+        <v>726</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>84</v>
@@ -18205,16 +18310,16 @@
         <v>84</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>699</v>
+        <v>727</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>700</v>
+        <v>728</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>701</v>
+        <v>729</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>702</v>
+        <v>730</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -18305,10 +18410,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>703</v>
+        <v>731</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>704</v>
+        <v>732</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18429,10 +18534,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>705</v>
+        <v>733</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>706</v>
+        <v>734</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18553,10 +18658,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>707</v>
+        <v>735</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>708</v>
+        <v>736</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18596,7 +18701,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>709</v>
+        <v>737</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>84</v>
@@ -18679,10 +18784,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>710</v>
+        <v>738</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>711</v>
+        <v>739</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18705,13 +18810,13 @@
         <v>84</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>712</v>
+        <v>740</v>
       </c>
       <c r="L123" t="s" s="2">
         <v>172</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>277</v>
+        <v>741</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -18771,19 +18876,19 @@
         <v>93</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>279</v>
+        <v>742</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>713</v>
+        <v>743</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>714</v>
+        <v>744</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>715</v>
+        <v>745</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>675</v>
+        <v>703</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>84</v>
@@ -18803,10 +18908,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>716</v>
+        <v>746</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>716</v>
+        <v>746</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18829,17 +18934,17 @@
         <v>94</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>717</v>
+        <v>747</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>718</v>
+        <v>748</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>719</v>
+        <v>749</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -18864,13 +18969,13 @@
         <v>84</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>721</v>
+        <v>751</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>84</v>
@@ -18888,7 +18993,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>722</v>
+        <v>752</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18924,15 +19029,15 @@
         <v>84</v>
       </c>
       <c r="AR124" t="s" s="2">
-        <v>723</v>
+        <v>753</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>724</v>
+        <v>754</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>724</v>
+        <v>754</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18955,19 +19060,19 @@
         <v>94</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>725</v>
+        <v>755</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>726</v>
+        <v>756</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>727</v>
+        <v>757</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>728</v>
+        <v>758</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>729</v>
+        <v>759</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
@@ -19004,7 +19109,7 @@
         <v>84</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="AC125" s="2"/>
       <c r="AD125" t="s" s="2">
@@ -19014,7 +19119,7 @@
         <v>143</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>730</v>
+        <v>760</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -19044,24 +19149,24 @@
         <v>84</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>687</v>
+        <v>715</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR125" t="s" s="2">
-        <v>731</v>
+        <v>761</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>732</v>
+        <v>762</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>724</v>
+        <v>754</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>733</v>
+        <v>763</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>84</v>
@@ -19083,19 +19188,19 @@
         <v>94</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>734</v>
+        <v>764</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>726</v>
+        <v>756</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>727</v>
+        <v>757</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>728</v>
+        <v>758</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>729</v>
+        <v>759</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -19144,7 +19249,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>730</v>
+        <v>760</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -19174,21 +19279,21 @@
         <v>84</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>687</v>
+        <v>715</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>731</v>
+        <v>761</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>735</v>
+        <v>765</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>736</v>
+        <v>766</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19309,10 +19414,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>737</v>
+        <v>767</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>738</v>
+        <v>768</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19435,10 +19540,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>739</v>
+        <v>769</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19461,19 +19566,19 @@
         <v>94</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>741</v>
+        <v>771</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>742</v>
+        <v>772</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>743</v>
+        <v>773</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>744</v>
+        <v>774</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>745</v>
+        <v>775</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19522,7 +19627,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>746</v>
+        <v>776</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19534,16 +19639,16 @@
         <v>84</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>747</v>
+        <v>777</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>748</v>
+        <v>778</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>715</v>
+        <v>745</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>675</v>
+        <v>703</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>84</v>
@@ -19552,21 +19657,21 @@
         <v>84</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>749</v>
+        <v>779</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR129" t="s" s="2">
-        <v>750</v>
+        <v>780</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>751</v>
+        <v>781</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>752</v>
+        <v>782</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19592,20 +19697,20 @@
         <v>114</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>753</v>
+        <v>783</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>754</v>
+        <v>784</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>755</v>
+        <v>785</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q130" t="s" s="2">
-        <v>756</v>
+        <v>786</v>
       </c>
       <c r="R130" t="s" s="2">
         <v>84</v>
@@ -19626,13 +19731,13 @@
         <v>84</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>757</v>
+        <v>787</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>758</v>
+        <v>788</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>84</v>
@@ -19650,7 +19755,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>759</v>
+        <v>789</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19680,21 +19785,21 @@
         <v>84</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>760</v>
+        <v>790</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR130" t="s" s="2">
-        <v>761</v>
+        <v>791</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>762</v>
+        <v>792</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>763</v>
+        <v>793</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19720,14 +19825,14 @@
         <v>153</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>764</v>
+        <v>794</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>766</v>
+        <v>796</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>84</v>
@@ -19776,7 +19881,7 @@
         <v>84</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>767</v>
+        <v>797</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>82</v>
@@ -19791,13 +19896,13 @@
         <v>106</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>768</v>
+        <v>798</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>769</v>
+        <v>799</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>675</v>
+        <v>703</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>84</v>
@@ -19806,21 +19911,21 @@
         <v>84</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>770</v>
+        <v>800</v>
       </c>
       <c r="AQ131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR131" t="s" s="2">
-        <v>771</v>
+        <v>801</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>772</v>
+        <v>802</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>773</v>
+        <v>803</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19846,14 +19951,14 @@
         <v>108</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>774</v>
+        <v>804</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>775</v>
+        <v>805</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>776</v>
+        <v>806</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
@@ -19902,7 +20007,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>777</v>
+        <v>807</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -19911,7 +20016,7 @@
         <v>93</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>778</v>
+        <v>808</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>106</v>
@@ -19932,21 +20037,21 @@
         <v>84</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>779</v>
+        <v>809</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR132" t="s" s="2">
-        <v>771</v>
+        <v>801</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19972,16 +20077,16 @@
         <v>114</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>782</v>
+        <v>812</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>783</v>
+        <v>813</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>784</v>
+        <v>814</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>785</v>
+        <v>815</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
@@ -20030,7 +20135,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -20060,21 +20165,21 @@
         <v>84</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>787</v>
+        <v>817</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR133" t="s" s="2">
-        <v>771</v>
+        <v>801</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>788</v>
+        <v>818</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>788</v>
+        <v>818</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -20097,19 +20202,19 @@
         <v>94</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>789</v>
+        <v>819</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>790</v>
+        <v>820</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>791</v>
+        <v>821</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>792</v>
+        <v>822</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -20158,7 +20263,7 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>794</v>
+        <v>824</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
@@ -20188,21 +20293,21 @@
         <v>84</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>795</v>
+        <v>825</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR134" t="s" s="2">
-        <v>796</v>
+        <v>826</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20225,19 +20330,19 @@
         <v>94</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>798</v>
+        <v>828</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>799</v>
+        <v>829</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>800</v>
+        <v>830</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>801</v>
+        <v>831</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>802</v>
+        <v>832</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>84</v>
@@ -20286,7 +20391,7 @@
         <v>84</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>803</v>
+        <v>833</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>82</v>
@@ -20316,21 +20421,21 @@
         <v>84</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>804</v>
+        <v>834</v>
       </c>
       <c r="AQ135" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR135" t="s" s="2">
-        <v>805</v>
+        <v>835</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>806</v>
+        <v>836</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>806</v>
+        <v>836</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20353,19 +20458,19 @@
         <v>94</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>734</v>
+        <v>764</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>807</v>
+        <v>837</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>808</v>
+        <v>838</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>809</v>
+        <v>839</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>810</v>
+        <v>840</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>84</v>
@@ -20414,7 +20519,7 @@
         <v>84</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>811</v>
+        <v>841</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>82</v>
@@ -20444,7 +20549,7 @@
         <v>84</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>812</v>
+        <v>842</v>
       </c>
       <c r="AQ136" t="s" s="2">
         <v>84</v>
@@ -20455,10 +20560,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>813</v>
+        <v>843</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>813</v>
+        <v>843</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20481,17 +20586,17 @@
         <v>94</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>734</v>
+        <v>764</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>814</v>
+        <v>844</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>815</v>
+        <v>845</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" t="s" s="2">
-        <v>816</v>
+        <v>846</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>84</v>
@@ -20540,7 +20645,7 @@
         <v>84</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>817</v>
+        <v>847</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>82</v>
@@ -20570,7 +20675,7 @@
         <v>84</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>812</v>
+        <v>842</v>
       </c>
       <c r="AQ137" t="s" s="2">
         <v>84</v>
@@ -20581,10 +20686,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>818</v>
+        <v>848</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>818</v>
+        <v>848</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20607,13 +20712,13 @@
         <v>84</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>819</v>
+        <v>849</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>820</v>
+        <v>850</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -20664,7 +20769,7 @@
         <v>84</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>818</v>
+        <v>848</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>82</v>
@@ -20691,10 +20796,10 @@
         <v>84</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>822</v>
+        <v>852</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>823</v>
+        <v>853</v>
       </c>
       <c r="AQ138" t="s" s="2">
         <v>84</v>
@@ -20705,10 +20810,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>824</v>
+        <v>854</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>824</v>
+        <v>854</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20829,10 +20934,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>825</v>
+        <v>855</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>825</v>
+        <v>855</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20955,14 +21060,14 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>826</v>
+        <v>856</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>826</v>
+        <v>856</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -20984,16 +21089,16 @@
         <v>139</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>84</v>
@@ -21042,7 +21147,7 @@
         <v>84</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>82</v>
@@ -21083,10 +21188,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>827</v>
+        <v>857</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>827</v>
+        <v>857</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -21109,16 +21214,16 @@
         <v>84</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>819</v>
+        <v>849</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>828</v>
+        <v>858</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>829</v>
+        <v>859</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>830</v>
+        <v>860</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -21168,7 +21273,7 @@
         <v>84</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>827</v>
+        <v>857</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>82</v>
@@ -21198,7 +21303,7 @@
         <v>84</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>831</v>
+        <v>861</v>
       </c>
       <c r="AQ142" t="s" s="2">
         <v>84</v>
@@ -21209,10 +21314,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>832</v>
+        <v>862</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>832</v>
+        <v>862</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21333,10 +21438,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>833</v>
+        <v>863</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>833</v>
+        <v>863</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21459,14 +21564,14 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>834</v>
+        <v>864</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>834</v>
+        <v>864</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -21488,16 +21593,16 @@
         <v>139</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="N145" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>84</v>
@@ -21546,7 +21651,7 @@
         <v>84</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>82</v>
@@ -21587,10 +21692,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>835</v>
+        <v>865</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>835</v>
+        <v>865</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21613,13 +21718,13 @@
         <v>84</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>734</v>
+        <v>764</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>836</v>
+        <v>866</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>837</v>
+        <v>867</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -21670,7 +21775,7 @@
         <v>84</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>835</v>
+        <v>865</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>82</v>
@@ -21700,7 +21805,7 @@
         <v>84</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>838</v>
+        <v>868</v>
       </c>
       <c r="AQ146" t="s" s="2">
         <v>84</v>
@@ -21711,10 +21816,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>839</v>
+        <v>869</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>839</v>
+        <v>869</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21737,13 +21842,13 @@
         <v>84</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>841</v>
+        <v>871</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>842</v>
+        <v>872</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -21794,7 +21899,7 @@
         <v>84</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>839</v>
+        <v>869</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>82</v>
@@ -21824,7 +21929,7 @@
         <v>84</v>
       </c>
       <c r="AP147" t="s" s="2">
-        <v>843</v>
+        <v>873</v>
       </c>
       <c r="AQ147" t="s" s="2">
         <v>84</v>
@@ -21835,10 +21940,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>844</v>
+        <v>874</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>844</v>
+        <v>874</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21861,13 +21966,13 @@
         <v>84</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>845</v>
+        <v>875</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>846</v>
+        <v>876</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -21918,7 +22023,7 @@
         <v>84</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>844</v>
+        <v>874</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>82</v>
@@ -21948,7 +22053,7 @@
         <v>84</v>
       </c>
       <c r="AP148" t="s" s="2">
-        <v>843</v>
+        <v>873</v>
       </c>
       <c r="AQ148" t="s" s="2">
         <v>84</v>
@@ -21959,10 +22064,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>847</v>
+        <v>877</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>847</v>
+        <v>877</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21985,19 +22090,19 @@
         <v>84</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>848</v>
+        <v>330</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>849</v>
+        <v>878</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>850</v>
+        <v>879</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>851</v>
+        <v>880</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>852</v>
+        <v>881</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>84</v>
@@ -22046,7 +22151,7 @@
         <v>84</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>847</v>
+        <v>877</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>82</v>
@@ -22073,10 +22178,10 @@
         <v>84</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>853</v>
+        <v>882</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>854</v>
+        <v>883</v>
       </c>
       <c r="AQ149" t="s" s="2">
         <v>84</v>
@@ -22087,10 +22192,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>855</v>
+        <v>884</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>855</v>
+        <v>884</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22211,10 +22316,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>856</v>
+        <v>885</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>856</v>
+        <v>885</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22337,10 +22442,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>857</v>
+        <v>886</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>857</v>
+        <v>886</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22366,13 +22471,13 @@
         <v>242</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>858</v>
+        <v>887</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>859</v>
+        <v>888</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>860</v>
+        <v>889</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -22422,7 +22527,7 @@
         <v>84</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>861</v>
+        <v>890</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>82</v>
@@ -22431,7 +22536,7 @@
         <v>93</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>862</v>
+        <v>891</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>106</v>
@@ -22452,21 +22557,21 @@
         <v>84</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>863</v>
+        <v>892</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR152" t="s" s="2">
-        <v>864</v>
+        <v>893</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>865</v>
+        <v>894</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>865</v>
+        <v>894</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22492,20 +22597,20 @@
         <v>242</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>866</v>
+        <v>895</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>867</v>
+        <v>896</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>868</v>
+        <v>897</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q153" t="s" s="2">
-        <v>869</v>
+        <v>898</v>
       </c>
       <c r="R153" t="s" s="2">
         <v>84</v>
@@ -22550,7 +22655,7 @@
         <v>84</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>870</v>
+        <v>899</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>82</v>
@@ -22559,19 +22664,19 @@
         <v>93</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>862</v>
+        <v>891</v>
       </c>
       <c r="AJ153" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>871</v>
+        <v>900</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>872</v>
+        <v>901</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>84</v>
@@ -22580,21 +22685,21 @@
         <v>84</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>873</v>
+        <v>902</v>
       </c>
       <c r="AQ153" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR153" t="s" s="2">
-        <v>874</v>
+        <v>903</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>875</v>
+        <v>904</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>875</v>
+        <v>904</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22617,16 +22722,16 @@
         <v>84</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>876</v>
+        <v>905</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>877</v>
+        <v>906</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>878</v>
+        <v>907</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>879</v>
+        <v>908</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -22676,7 +22781,7 @@
         <v>84</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>875</v>
+        <v>904</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>82</v>
@@ -22691,36 +22796,36 @@
         <v>106</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>880</v>
+        <v>909</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>881</v>
+        <v>910</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>882</v>
+        <v>911</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>883</v>
+        <v>912</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>884</v>
+        <v>913</v>
       </c>
       <c r="AQ154" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR154" t="s" s="2">
-        <v>885</v>
+        <v>914</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>886</v>
+        <v>915</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>886</v>
+        <v>915</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22743,13 +22848,13 @@
         <v>84</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>734</v>
+        <v>764</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>887</v>
+        <v>916</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>888</v>
+        <v>917</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -22800,7 +22905,7 @@
         <v>84</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>886</v>
+        <v>915</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>82</v>
@@ -22827,24 +22932,24 @@
         <v>84</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>889</v>
+        <v>918</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>890</v>
+        <v>919</v>
       </c>
       <c r="AQ155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR155" t="s" s="2">
-        <v>891</v>
+        <v>920</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>892</v>
+        <v>921</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>892</v>
+        <v>921</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22965,10 +23070,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>893</v>
+        <v>922</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>893</v>
+        <v>922</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23091,10 +23196,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>894</v>
+        <v>923</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>894</v>
+        <v>923</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23117,19 +23222,19 @@
         <v>94</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>741</v>
+        <v>771</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>742</v>
+        <v>772</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>743</v>
+        <v>773</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>744</v>
+        <v>774</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>745</v>
+        <v>775</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>84</v>
@@ -23178,7 +23283,7 @@
         <v>84</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>746</v>
+        <v>776</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>82</v>
@@ -23193,13 +23298,13 @@
         <v>106</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>895</v>
+        <v>924</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>896</v>
+        <v>925</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>84</v>
@@ -23208,21 +23313,21 @@
         <v>84</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>749</v>
+        <v>779</v>
       </c>
       <c r="AQ158" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR158" t="s" s="2">
-        <v>750</v>
+        <v>780</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>897</v>
+        <v>926</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>897</v>
+        <v>926</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23248,20 +23353,20 @@
         <v>114</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>753</v>
+        <v>783</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>754</v>
+        <v>784</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>755</v>
+        <v>785</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q159" t="s" s="2">
-        <v>756</v>
+        <v>786</v>
       </c>
       <c r="R159" t="s" s="2">
         <v>84</v>
@@ -23282,13 +23387,13 @@
         <v>84</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>757</v>
+        <v>787</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>758</v>
+        <v>788</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>84</v>
@@ -23306,7 +23411,7 @@
         <v>84</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>759</v>
+        <v>789</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>82</v>
@@ -23336,21 +23441,21 @@
         <v>84</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>760</v>
+        <v>790</v>
       </c>
       <c r="AQ159" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR159" t="s" s="2">
-        <v>761</v>
+        <v>791</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>898</v>
+        <v>927</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>898</v>
+        <v>927</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23376,14 +23481,14 @@
         <v>153</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>764</v>
+        <v>794</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>765</v>
+        <v>795</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>766</v>
+        <v>796</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>84</v>
@@ -23432,7 +23537,7 @@
         <v>84</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>767</v>
+        <v>797</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
@@ -23462,21 +23567,21 @@
         <v>84</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>770</v>
+        <v>800</v>
       </c>
       <c r="AQ160" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR160" t="s" s="2">
-        <v>771</v>
+        <v>801</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>899</v>
+        <v>928</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>899</v>
+        <v>928</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23502,14 +23607,14 @@
         <v>108</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>774</v>
+        <v>804</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>775</v>
+        <v>805</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>776</v>
+        <v>806</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>84</v>
@@ -23558,7 +23663,7 @@
         <v>84</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>777</v>
+        <v>807</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>82</v>
@@ -23567,7 +23672,7 @@
         <v>93</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>778</v>
+        <v>808</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>106</v>
@@ -23588,21 +23693,21 @@
         <v>84</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>779</v>
+        <v>809</v>
       </c>
       <c r="AQ161" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR161" t="s" s="2">
-        <v>771</v>
+        <v>801</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>900</v>
+        <v>929</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>900</v>
+        <v>929</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23628,16 +23733,16 @@
         <v>114</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>782</v>
+        <v>812</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>783</v>
+        <v>813</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>784</v>
+        <v>814</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>785</v>
+        <v>815</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>84</v>
@@ -23686,7 +23791,7 @@
         <v>84</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23716,21 +23821,21 @@
         <v>84</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>787</v>
+        <v>817</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR162" t="s" s="2">
-        <v>771</v>
+        <v>801</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>901</v>
+        <v>930</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>901</v>
+        <v>930</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23753,16 +23858,16 @@
         <v>84</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>902</v>
+        <v>931</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>903</v>
+        <v>932</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>904</v>
+        <v>933</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -23812,7 +23917,7 @@
         <v>84</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>901</v>
+        <v>930</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>82</v>
@@ -23827,22 +23932,22 @@
         <v>106</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>905</v>
+        <v>934</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>906</v>
+        <v>935</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>907</v>
+        <v>936</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>908</v>
+        <v>937</v>
       </c>
       <c r="AQ163" t="s" s="2">
         <v>84</v>
@@ -23853,10 +23958,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>909</v>
+        <v>938</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>909</v>
+        <v>938</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23879,13 +23984,13 @@
         <v>84</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>910</v>
+        <v>337</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>911</v>
+        <v>939</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>912</v>
+        <v>940</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -23936,7 +24041,7 @@
         <v>84</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>909</v>
+        <v>938</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>82</v>
@@ -23966,10 +24071,10 @@
         <v>84</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>913</v>
+        <v>941</v>
       </c>
       <c r="AQ164" t="s" s="2">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="AR164" t="s" s="2">
         <v>84</v>
@@ -23977,10 +24082,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>914</v>
+        <v>942</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>914</v>
+        <v>942</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -24003,13 +24108,13 @@
         <v>84</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>819</v>
+        <v>849</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>915</v>
+        <v>943</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>916</v>
+        <v>944</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -24060,7 +24165,7 @@
         <v>84</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>914</v>
+        <v>942</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>82</v>
@@ -24087,10 +24192,10 @@
         <v>84</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>917</v>
+        <v>945</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>918</v>
+        <v>946</v>
       </c>
       <c r="AQ165" t="s" s="2">
         <v>84</v>
@@ -24101,10 +24206,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>919</v>
+        <v>947</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>919</v>
+        <v>947</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24225,10 +24330,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>920</v>
+        <v>948</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>920</v>
+        <v>948</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24351,14 +24456,14 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>921</v>
+        <v>949</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>921</v>
+        <v>949</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
@@ -24380,16 +24485,16 @@
         <v>139</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>84</v>
@@ -24438,7 +24543,7 @@
         <v>84</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -24479,10 +24584,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>922</v>
+        <v>950</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>922</v>
+        <v>950</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24505,16 +24610,16 @@
         <v>84</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>635</v>
+        <v>663</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>923</v>
+        <v>951</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>924</v>
+        <v>952</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>925</v>
+        <v>953</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -24540,13 +24645,13 @@
         <v>84</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>926</v>
+        <v>954</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>927</v>
+        <v>955</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>84</v>
@@ -24564,7 +24669,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>922</v>
+        <v>950</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>93</v>
@@ -24591,24 +24696,24 @@
         <v>84</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>917</v>
+        <v>945</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>928</v>
+        <v>956</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR169" t="s" s="2">
-        <v>929</v>
+        <v>957</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>930</v>
+        <v>958</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>930</v>
+        <v>958</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24631,13 +24736,13 @@
         <v>84</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>931</v>
+        <v>959</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>932</v>
+        <v>960</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -24664,13 +24769,13 @@
         <v>84</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>933</v>
+        <v>961</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>934</v>
+        <v>962</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>84</v>
@@ -24688,7 +24793,7 @@
         <v>84</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>930</v>
+        <v>958</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>82</v>
@@ -24715,24 +24820,24 @@
         <v>84</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>935</v>
+        <v>963</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>936</v>
+        <v>964</v>
       </c>
       <c r="AQ170" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR170" t="s" s="2">
-        <v>937</v>
+        <v>965</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>938</v>
+        <v>966</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>938</v>
+        <v>966</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24755,13 +24860,13 @@
         <v>84</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>939</v>
+        <v>967</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>940</v>
+        <v>968</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>941</v>
+        <v>969</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -24812,7 +24917,7 @@
         <v>84</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>938</v>
+        <v>966</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>82</v>
@@ -24836,13 +24941,13 @@
         <v>84</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>942</v>
+        <v>970</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>935</v>
+        <v>963</v>
       </c>
       <c r="AP171" t="s" s="2">
-        <v>943</v>
+        <v>971</v>
       </c>
       <c r="AQ171" t="s" s="2">
         <v>84</v>
@@ -24853,14 +24958,14 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>944</v>
+        <v>972</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>944</v>
+        <v>972</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>945</v>
+        <v>973</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
@@ -24879,16 +24984,16 @@
         <v>84</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>946</v>
+        <v>974</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>947</v>
+        <v>975</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>948</v>
+        <v>976</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>949</v>
+        <v>977</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -24938,7 +25043,7 @@
         <v>84</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>944</v>
+        <v>972</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>82</v>
@@ -24968,7 +25073,7 @@
         <v>84</v>
       </c>
       <c r="AP172" t="s" s="2">
-        <v>950</v>
+        <v>978</v>
       </c>
       <c r="AQ172" t="s" s="2">
         <v>84</v>
@@ -24979,10 +25084,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>951</v>
+        <v>979</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>951</v>
+        <v>979</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -25005,16 +25110,16 @@
         <v>84</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>952</v>
+        <v>980</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>953</v>
+        <v>981</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>954</v>
+        <v>982</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>955</v>
+        <v>983</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -25064,7 +25169,7 @@
         <v>84</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>951</v>
+        <v>979</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>82</v>
@@ -25088,13 +25193,13 @@
         <v>84</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>956</v>
+        <v>984</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP173" t="s" s="2">
-        <v>957</v>
+        <v>985</v>
       </c>
       <c r="AQ173" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -612,7 +612,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mro-27-1746-1:If (undefined) is P then fixed value http://va.gov/terminology/vistaDefinedTerms/52-100 {null}</t>
+mro-27-1746-1:If P then fixed value http://va.gov/terminology/vistaDefinedTerms/52-100 {true}</t>
   </si>
   <si>
     <t>1746-1: fixed value = http://va.gov/terminology/vistaDefinedTerms/52-100 if P</t>
@@ -667,7 +667,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mro-27-1746:If (52-11) is P then fixed value #active-parked {null}</t>
+mro-27-1746:If (52-11) is P then fixed value #active-parked {true}</t>
   </si>
   <si>
     <t>1746: fixed value = #active-parked when PRESCRIPTION - MAIL/WINDOW/PARK (52-11) if P</t>
@@ -2334,7 +2334,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mro-27-841:If not a number then source value from (52-113 &gt; 52.0113-.01) {null}</t>
+mro-27-841:If not a number then source value from (52-113 &gt; 52.0113-.01) {true}</t>
   </si>
   <si>
     <t>841: source value based on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) if not a number</t>
@@ -2440,7 +2440,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mro-27-811:If number then source value from (52-113 &gt; 52.0113-.01) {null}</t>
+mro-27-811:If number then source value from (52-113 &gt; 52.0113-.01) {true}</t>
   </si>
   <si>
     <t>811: source value based on PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) if number</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
